--- a/barRace/chattersRace2026.xlsx
+++ b/barRace/chattersRace2026.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM56"/>
+  <dimension ref="A1:BC57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -551,10 +551,58 @@
       <c r="AM1" s="2" t="n">
         <v>46069</v>
       </c>
+      <c r="AN1" s="2" t="n">
+        <v>46070</v>
+      </c>
+      <c r="AO1" s="2" t="n">
+        <v>46074</v>
+      </c>
+      <c r="AP1" s="2" t="n">
+        <v>46075</v>
+      </c>
+      <c r="AQ1" s="2" t="n">
+        <v>46076</v>
+      </c>
+      <c r="AR1" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="AS1" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="AT1" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="AU1" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="AV1" s="2" t="n">
+        <v>46082</v>
+      </c>
+      <c r="AW1" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="AX1" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="AY1" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="AZ1" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="BA1" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="BB1" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="BC1" s="2" t="n">
+        <v>46090</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -672,10 +720,58 @@
       <c r="AM2" t="n">
         <v>1967</v>
       </c>
+      <c r="AN2" t="n">
+        <v>1984</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>2061</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>2147</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>2195</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>2231</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>2298</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>2433</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>2500</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>2581</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>2650</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>2664</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>2731</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>2804</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>2854</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>2907</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>2955</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -793,10 +889,58 @@
       <c r="AM3" t="n">
         <v>153</v>
       </c>
+      <c r="AN3" t="n">
+        <v>153</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>153</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>153</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>153</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>157</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>157</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>157</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>162</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>162</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>162</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>162</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>162</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>162</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -914,10 +1058,58 @@
       <c r="AM4" t="n">
         <v>4220</v>
       </c>
+      <c r="AN4" t="n">
+        <v>4308</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4323</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>4323</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>4398</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>4549</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>4549</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>4679</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>4679</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>4679</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>4679</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>4679</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>4679</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4679</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>4714</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>4716</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4716</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1035,10 +1227,58 @@
       <c r="AM5" t="n">
         <v>3138</v>
       </c>
+      <c r="AN5" t="n">
+        <v>3158</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>3222</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>3292</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>3372</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>3418</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>3514</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>3574</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>3638</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>3731</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>3781</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>3914</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>4056</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4168</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>4203</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>4259</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4307</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1156,10 +1396,58 @@
       <c r="AM6" t="n">
         <v>5870</v>
       </c>
+      <c r="AN6" t="n">
+        <v>5972</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>6409</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>6906</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>7214</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>7392</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7871</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>8487</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>8882</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>9491</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>9912</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>10356</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>11066</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>11407</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>11449</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>12163</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>12769</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>114</v>
+        <v>145</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1277,10 +1565,58 @@
       <c r="AM7" t="n">
         <v>3060</v>
       </c>
+      <c r="AN7" t="n">
+        <v>3060</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>3076</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3078</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>3089</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>3089</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>3089</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>3089</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>3101</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>3377</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>3387</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>3387</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>3387</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>3387</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>3422</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>3487</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>3487</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1398,10 +1734,58 @@
       <c r="AM8" t="n">
         <v>8220</v>
       </c>
+      <c r="AN8" t="n">
+        <v>8220</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>8714</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>9107</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9285</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>9463</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>9538</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>10231</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>10845</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>11360</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>11360</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>11384</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>11384</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>11842</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>12317</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>12813</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>13156</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>157</v>
+        <v>197</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1519,10 +1903,58 @@
       <c r="AM9" t="n">
         <v>920</v>
       </c>
+      <c r="AN9" t="n">
+        <v>920</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>930</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>949</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>986</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>992</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1011</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1028</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1043</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1049</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>1058</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1084</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>1084</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>1114</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>1114</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1115</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>1134</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>159</v>
+        <v>201</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1640,10 +2072,58 @@
       <c r="AM10" t="n">
         <v>4501</v>
       </c>
+      <c r="AN10" t="n">
+        <v>4539</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>4660</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>4797</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>4995</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>5097</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>5198</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>5350</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>5514</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>5975</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>6174</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>6283</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>6449</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>6596</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>6748</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7039</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>7180</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>165</v>
+        <v>209</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1761,10 +2241,58 @@
       <c r="AM11" t="n">
         <v>3063</v>
       </c>
+      <c r="AN11" t="n">
+        <v>3063</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>3133</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>3313</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>3382</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>3408</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>3509</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>3702</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>3869</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>3983</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>4055</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>4172</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>4270</v>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4330</v>
+      </c>
+      <c r="BA11" t="n">
+        <v>4386</v>
+      </c>
+      <c r="BB11" t="n">
+        <v>4509</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4554</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>166</v>
+        <v>210</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1882,10 +2410,58 @@
       <c r="AM12" t="n">
         <v>13183</v>
       </c>
+      <c r="AN12" t="n">
+        <v>13232</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>13409</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>13661</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>14012</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>14157</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>14377</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>14972</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>15398</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>15828</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>16147</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>16607</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>16951</v>
+      </c>
+      <c r="AZ12" t="n">
+        <v>17282</v>
+      </c>
+      <c r="BA12" t="n">
+        <v>17621</v>
+      </c>
+      <c r="BB12" t="n">
+        <v>18097</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>18480</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2003,10 +2579,58 @@
       <c r="AM13" t="n">
         <v>3541</v>
       </c>
+      <c r="AN13" t="n">
+        <v>3541</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>3620</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>3626</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>3691</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>3728</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>3810</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>3918</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>3941</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>4050</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>4110</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>4156</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>4279</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>4397</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>4478</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>4545</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4606</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>229</v>
+        <v>292</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2124,10 +2748,58 @@
       <c r="AM14" t="n">
         <v>7617</v>
       </c>
+      <c r="AN14" t="n">
+        <v>7617</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>7617</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>7809</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>7964</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>8078</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8413</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>8413</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>8413</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>8413</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>8437</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>8447</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>8739</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>8739</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>8822</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9031</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>9127</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>242</v>
+        <v>311</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2245,10 +2917,58 @@
       <c r="AM15" t="n">
         <v>9750</v>
       </c>
+      <c r="AN15" t="n">
+        <v>9854</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>9986</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>9997</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>10145</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>10239</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>10548</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>10965</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>11244</v>
+      </c>
+      <c r="AV15" t="n">
+        <v>11518</v>
+      </c>
+      <c r="AW15" t="n">
+        <v>11747</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>11881</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>12076</v>
+      </c>
+      <c r="AZ15" t="n">
+        <v>12092</v>
+      </c>
+      <c r="BA15" t="n">
+        <v>12097</v>
+      </c>
+      <c r="BB15" t="n">
+        <v>12156</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>12278</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>245</v>
+        <v>316</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2366,10 +3086,58 @@
       <c r="AM16" t="n">
         <v>3113</v>
       </c>
+      <c r="AN16" t="n">
+        <v>3135</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>3177</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>3248</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>3299</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>3328</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>3461</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>3614</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>3652</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>3758</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>3831</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>3947</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>3982</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>4080</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>4171</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>4240</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4298</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>249</v>
+        <v>321</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2487,10 +3255,58 @@
       <c r="AM17" t="n">
         <v>1448</v>
       </c>
+      <c r="AN17" t="n">
+        <v>1448</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>1451</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1451</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1451</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1469</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1473</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1509</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1588</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>1611</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>1611</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1624</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>1668</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>1676</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>1676</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>1692</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>1692</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>282</v>
+        <v>359</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -2608,10 +3424,58 @@
       <c r="AM18" t="n">
         <v>2311</v>
       </c>
+      <c r="AN18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>2311</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>2331</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>2331</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>2331</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>2331</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>311</v>
+        <v>393</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2729,10 +3593,58 @@
       <c r="AM19" t="n">
         <v>6927</v>
       </c>
+      <c r="AN19" t="n">
+        <v>6930</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>7168</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>7505</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>7653</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>7752</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>7975</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>8354</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>8517</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>8568</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>8772</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>8851</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>9102</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>9399</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>9535</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>9593</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>9770</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>337</v>
+        <v>425</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -2850,10 +3762,58 @@
       <c r="AM20" t="n">
         <v>3735</v>
       </c>
+      <c r="AN20" t="n">
+        <v>3735</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>3788</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>3788</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>3788</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>3788</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>3788</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>4110</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>4110</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4436</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4475</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>4482</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>4507</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>4546</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4586</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4597</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>4597</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>364</v>
+        <v>459</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -2971,10 +3931,58 @@
       <c r="AM21" t="n">
         <v>1827</v>
       </c>
+      <c r="AN21" t="n">
+        <v>1827</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>1953</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>2046</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>2046</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>2127</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>2136</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>2190</v>
+      </c>
+      <c r="AV21" t="n">
+        <v>2211</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>2229</v>
+      </c>
+      <c r="AX21" t="n">
+        <v>2229</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>2264</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>2275</v>
+      </c>
+      <c r="BA21" t="n">
+        <v>2314</v>
+      </c>
+      <c r="BB21" t="n">
+        <v>2391</v>
+      </c>
+      <c r="BC21" t="n">
+        <v>2395</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>415</v>
+        <v>525</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -3092,10 +4100,58 @@
       <c r="AM22" t="n">
         <v>8688</v>
       </c>
+      <c r="AN22" t="n">
+        <v>8764</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>8999</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>9214</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>9387</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>9489</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>9721</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>9968</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>10150</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>10351</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>10491</v>
+      </c>
+      <c r="AX22" t="n">
+        <v>10644</v>
+      </c>
+      <c r="AY22" t="n">
+        <v>10856</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>11025</v>
+      </c>
+      <c r="BA22" t="n">
+        <v>11207</v>
+      </c>
+      <c r="BB22" t="n">
+        <v>11591</v>
+      </c>
+      <c r="BC22" t="n">
+        <v>11743</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>432</v>
+        <v>545</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -3213,10 +4269,58 @@
       <c r="AM23" t="n">
         <v>1393</v>
       </c>
+      <c r="AN23" t="n">
+        <v>1393</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>1393</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1393</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>1402</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1402</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1402</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1402</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1402</v>
+      </c>
+      <c r="AV23" t="n">
+        <v>1408</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>1408</v>
+      </c>
+      <c r="AX23" t="n">
+        <v>1408</v>
+      </c>
+      <c r="AY23" t="n">
+        <v>1411</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>1411</v>
+      </c>
+      <c r="BA23" t="n">
+        <v>1494</v>
+      </c>
+      <c r="BB23" t="n">
+        <v>1511</v>
+      </c>
+      <c r="BC23" t="n">
+        <v>1516</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>459</v>
+        <v>578</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -3334,10 +4438,58 @@
       <c r="AM24" t="n">
         <v>181</v>
       </c>
+      <c r="AN24" t="n">
+        <v>181</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>181</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>181</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>181</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>192</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>192</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>214</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>214</v>
+      </c>
+      <c r="AV24" t="n">
+        <v>214</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>214</v>
+      </c>
+      <c r="AX24" t="n">
+        <v>214</v>
+      </c>
+      <c r="AY24" t="n">
+        <v>214</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>218</v>
+      </c>
+      <c r="BA24" t="n">
+        <v>218</v>
+      </c>
+      <c r="BB24" t="n">
+        <v>218</v>
+      </c>
+      <c r="BC24" t="n">
+        <v>222</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>477</v>
+        <v>597</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -3455,10 +4607,58 @@
       <c r="AM25" t="n">
         <v>6213</v>
       </c>
+      <c r="AN25" t="n">
+        <v>6242</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>6329</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>6486</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>6720</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>6884</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>7104</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>7282</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>7380</v>
+      </c>
+      <c r="AV25" t="n">
+        <v>7580</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>7807</v>
+      </c>
+      <c r="AX25" t="n">
+        <v>7961</v>
+      </c>
+      <c r="AY25" t="n">
+        <v>8275</v>
+      </c>
+      <c r="AZ25" t="n">
+        <v>8611</v>
+      </c>
+      <c r="BA25" t="n">
+        <v>8638</v>
+      </c>
+      <c r="BB25" t="n">
+        <v>8963</v>
+      </c>
+      <c r="BC25" t="n">
+        <v>9116</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>546</v>
+        <v>681</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -3576,10 +4776,58 @@
       <c r="AM26" t="n">
         <v>17044</v>
       </c>
+      <c r="AN26" t="n">
+        <v>17132</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>17421</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>17793</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>18199</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>18386</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>18749</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>19334</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>19850</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>20478</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>20850</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>21447</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>21770</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>22101</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>22490</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>22973</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>23360</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>547</v>
+        <v>682</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3697,10 +4945,58 @@
       <c r="AM27" t="n">
         <v>712</v>
       </c>
+      <c r="AN27" t="n">
+        <v>712</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>712</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>722</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>722</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>722</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>722</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>722</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>722</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>751</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>751</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>751</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>751</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>751</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>751</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>755</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>557</v>
+        <v>695</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3818,10 +5114,58 @@
       <c r="AM28" t="n">
         <v>5353</v>
       </c>
+      <c r="AN28" t="n">
+        <v>5383</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>5543</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>5750</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>5905</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>6014</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>6144</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>6432</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>6633</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>6801</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>6953</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>7009</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>7139</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>7345</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>7488</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>7719</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>7951</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>642</v>
+        <v>794</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3939,10 +5283,58 @@
       <c r="AM29" t="n">
         <v>442</v>
       </c>
+      <c r="AN29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>442</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>448</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>450</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>450</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>450</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>450</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>727</v>
+        <v>893</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -4060,10 +5452,58 @@
       <c r="AM30" t="n">
         <v>11123</v>
       </c>
+      <c r="AN30" t="n">
+        <v>11123</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>11157</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>11157</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>11323</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>11369</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>11466</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>11699</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>11706</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>11706</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>11706</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>11950</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>11950</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>11959</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>12171</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>12306</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>12306</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>813</v>
+        <v>994</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -4181,10 +5621,58 @@
       <c r="AM31" t="n">
         <v>10955</v>
       </c>
+      <c r="AN31" t="n">
+        <v>10990</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>11665</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>12088</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>12966</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>13307</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>13994</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>14858</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>15795</v>
+      </c>
+      <c r="AV31" t="n">
+        <v>16900</v>
+      </c>
+      <c r="AW31" t="n">
+        <v>17213</v>
+      </c>
+      <c r="AX31" t="n">
+        <v>18196</v>
+      </c>
+      <c r="AY31" t="n">
+        <v>18497</v>
+      </c>
+      <c r="AZ31" t="n">
+        <v>18920</v>
+      </c>
+      <c r="BA31" t="n">
+        <v>19321</v>
+      </c>
+      <c r="BB31" t="n">
+        <v>19362</v>
+      </c>
+      <c r="BC31" t="n">
+        <v>19856</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>861</v>
+        <v>1050</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -4302,10 +5790,58 @@
       <c r="AM32" t="n">
         <v>15281</v>
       </c>
+      <c r="AN32" t="n">
+        <v>15324</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>15378</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>15662</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>15662</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>15663</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>16290</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>16763</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>17404</v>
+      </c>
+      <c r="AV32" t="n">
+        <v>17972</v>
+      </c>
+      <c r="AW32" t="n">
+        <v>18388</v>
+      </c>
+      <c r="AX32" t="n">
+        <v>19394</v>
+      </c>
+      <c r="AY32" t="n">
+        <v>19914</v>
+      </c>
+      <c r="AZ32" t="n">
+        <v>20780</v>
+      </c>
+      <c r="BA32" t="n">
+        <v>21308</v>
+      </c>
+      <c r="BB32" t="n">
+        <v>21519</v>
+      </c>
+      <c r="BC32" t="n">
+        <v>21871</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>872</v>
+        <v>1062</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -4423,10 +5959,58 @@
       <c r="AM33" t="n">
         <v>15228</v>
       </c>
+      <c r="AN33" t="n">
+        <v>15305</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>15620</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>16105</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>16421</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>16571</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>17109</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>18132</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>18762</v>
+      </c>
+      <c r="AV33" t="n">
+        <v>19424</v>
+      </c>
+      <c r="AW33" t="n">
+        <v>19800</v>
+      </c>
+      <c r="AX33" t="n">
+        <v>20421</v>
+      </c>
+      <c r="AY33" t="n">
+        <v>20690</v>
+      </c>
+      <c r="AZ33" t="n">
+        <v>21368</v>
+      </c>
+      <c r="BA33" t="n">
+        <v>21810</v>
+      </c>
+      <c r="BB33" t="n">
+        <v>22379</v>
+      </c>
+      <c r="BC33" t="n">
+        <v>22895</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>873</v>
+        <v>1065</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -4544,10 +6128,58 @@
       <c r="AM34" t="n">
         <v>2750</v>
       </c>
+      <c r="AN34" t="n">
+        <v>2753</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>2816</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>2816</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>2816</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>2816</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>2816</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>2854</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>3129</v>
+      </c>
+      <c r="AV34" t="n">
+        <v>3154</v>
+      </c>
+      <c r="AW34" t="n">
+        <v>3200</v>
+      </c>
+      <c r="AX34" t="n">
+        <v>3219</v>
+      </c>
+      <c r="AY34" t="n">
+        <v>3219</v>
+      </c>
+      <c r="AZ34" t="n">
+        <v>3518</v>
+      </c>
+      <c r="BA34" t="n">
+        <v>3739</v>
+      </c>
+      <c r="BB34" t="n">
+        <v>3853</v>
+      </c>
+      <c r="BC34" t="n">
+        <v>3878</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>952</v>
+        <v>1170</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -4665,10 +6297,58 @@
       <c r="AM35" t="n">
         <v>2480</v>
       </c>
+      <c r="AN35" t="n">
+        <v>2504</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>2511</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>2516</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>2542</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>2571</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>2622</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>2662</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>2690</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>2707</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>2837</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>2982</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>3032</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>3125</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>3216</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>3336</v>
+      </c>
+      <c r="BC35" t="n">
+        <v>3450</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>963</v>
+        <v>1181</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -4786,135 +6466,231 @@
       <c r="AM36" t="n">
         <v>51</v>
       </c>
+      <c r="AN36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AU36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AV36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AW36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AX36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AY36" t="n">
+        <v>51</v>
+      </c>
+      <c r="AZ36" t="n">
+        <v>51</v>
+      </c>
+      <c r="BA36" t="n">
+        <v>51</v>
+      </c>
+      <c r="BB36" t="n">
+        <v>51</v>
+      </c>
+      <c r="BC36" t="n">
+        <v>51</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>1029</v>
+        <v>1267</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>yippyyoyippyyay</t>
+          <t>yop2u</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="D37" t="n">
-        <v>22</v>
+        <v>132</v>
       </c>
       <c r="E37" t="n">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="F37" t="n">
-        <v>37</v>
+        <v>157</v>
       </c>
       <c r="G37" t="n">
-        <v>56</v>
+        <v>180</v>
       </c>
       <c r="H37" t="n">
-        <v>68</v>
+        <v>186</v>
       </c>
       <c r="I37" t="n">
-        <v>160</v>
+        <v>286</v>
       </c>
       <c r="J37" t="n">
-        <v>160</v>
+        <v>288</v>
       </c>
       <c r="K37" t="n">
-        <v>169</v>
+        <v>289</v>
       </c>
       <c r="L37" t="n">
-        <v>170</v>
+        <v>289</v>
       </c>
       <c r="M37" t="n">
-        <v>170</v>
+        <v>293</v>
       </c>
       <c r="N37" t="n">
-        <v>170</v>
+        <v>293</v>
       </c>
       <c r="O37" t="n">
-        <v>175</v>
+        <v>293</v>
       </c>
       <c r="P37" t="n">
-        <v>276</v>
+        <v>367</v>
       </c>
       <c r="Q37" t="n">
-        <v>283</v>
+        <v>386</v>
       </c>
       <c r="R37" t="n">
-        <v>283</v>
+        <v>405</v>
       </c>
       <c r="S37" t="n">
-        <v>302</v>
+        <v>454</v>
       </c>
       <c r="T37" t="n">
-        <v>302</v>
+        <v>462</v>
       </c>
       <c r="U37" t="n">
-        <v>304</v>
+        <v>477</v>
       </c>
       <c r="V37" t="n">
-        <v>305</v>
+        <v>516</v>
       </c>
       <c r="W37" t="n">
-        <v>305</v>
+        <v>529</v>
       </c>
       <c r="X37" t="n">
-        <v>305</v>
+        <v>541</v>
       </c>
       <c r="Y37" t="n">
-        <v>319</v>
+        <v>547</v>
       </c>
       <c r="Z37" t="n">
-        <v>319</v>
+        <v>557</v>
       </c>
       <c r="AA37" t="n">
-        <v>319</v>
+        <v>564</v>
       </c>
       <c r="AB37" t="n">
-        <v>319</v>
+        <v>568</v>
       </c>
       <c r="AC37" t="n">
-        <v>322</v>
+        <v>573</v>
       </c>
       <c r="AD37" t="n">
-        <v>322</v>
+        <v>580</v>
       </c>
       <c r="AE37" t="n">
-        <v>324</v>
+        <v>587</v>
       </c>
       <c r="AF37" t="n">
-        <v>335</v>
+        <v>587</v>
       </c>
       <c r="AG37" t="n">
-        <v>341</v>
+        <v>591</v>
       </c>
       <c r="AH37" t="n">
-        <v>347</v>
+        <v>592</v>
       </c>
       <c r="AI37" t="n">
-        <v>348</v>
+        <v>592</v>
       </c>
       <c r="AJ37" t="n">
-        <v>362</v>
+        <v>592</v>
       </c>
       <c r="AK37" t="n">
-        <v>369</v>
+        <v>594</v>
       </c>
       <c r="AL37" t="n">
-        <v>382</v>
+        <v>594</v>
       </c>
       <c r="AM37" t="n">
-        <v>382</v>
+        <v>595</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>597</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>600</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>603</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>609</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>611</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>615</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>616</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>620</v>
+      </c>
+      <c r="AV37" t="n">
+        <v>623</v>
+      </c>
+      <c r="AW37" t="n">
+        <v>625</v>
+      </c>
+      <c r="AX37" t="n">
+        <v>625</v>
+      </c>
+      <c r="AY37" t="n">
+        <v>676</v>
+      </c>
+      <c r="AZ37" t="n">
+        <v>676</v>
+      </c>
+      <c r="BA37" t="n">
+        <v>676</v>
+      </c>
+      <c r="BB37" t="n">
+        <v>676</v>
+      </c>
+      <c r="BC37" t="n">
+        <v>677</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>1030</v>
+        <v>1272</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ylla</t>
+          <t>yrgakhosoo</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -4927,236 +6703,332 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
+        <v>1</v>
+      </c>
+      <c r="S38" t="n">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>6</v>
+      </c>
+      <c r="V38" t="n">
+        <v>6</v>
+      </c>
+      <c r="W38" t="n">
+        <v>13</v>
+      </c>
+      <c r="X38" t="n">
         <v>21</v>
       </c>
-      <c r="S38" t="n">
+      <c r="Y38" t="n">
         <v>21</v>
       </c>
-      <c r="T38" t="n">
+      <c r="Z38" t="n">
         <v>21</v>
       </c>
-      <c r="U38" t="n">
+      <c r="AA38" t="n">
         <v>21</v>
       </c>
-      <c r="V38" t="n">
+      <c r="AB38" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG38" t="n">
         <v>24</v>
       </c>
-      <c r="W38" t="n">
-        <v>25</v>
-      </c>
-      <c r="X38" t="n">
-        <v>25</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>29</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>29</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>29</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>29</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>29</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>29</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>29</v>
-      </c>
       <c r="AH38" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AI38" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AJ38" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AK38" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AL38" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="AM38" t="n">
-        <v>29</v>
+        <v>24</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>28</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>28</v>
+      </c>
+      <c r="BB38" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC38" t="n">
+        <v>28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>1031</v>
+        <v>1273</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>yop2u</t>
+          <t>yupbekha</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>132</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>135</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>286</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>288</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="L39" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>293</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>367</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>386</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>454</v>
+        <v>0</v>
       </c>
       <c r="T39" t="n">
-        <v>462</v>
+        <v>0</v>
       </c>
       <c r="U39" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>516</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>529</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>541</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>547</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>557</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>564</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>568</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>573</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>587</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>587</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
-        <v>591</v>
+        <v>0</v>
       </c>
       <c r="AH39" t="n">
-        <v>592</v>
+        <v>47</v>
       </c>
       <c r="AI39" t="n">
-        <v>592</v>
+        <v>47</v>
       </c>
       <c r="AJ39" t="n">
-        <v>592</v>
+        <v>47</v>
       </c>
       <c r="AK39" t="n">
-        <v>594</v>
+        <v>47</v>
       </c>
       <c r="AL39" t="n">
-        <v>594</v>
+        <v>47</v>
       </c>
       <c r="AM39" t="n">
-        <v>595</v>
+        <v>47</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AV39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AW39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AX39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AY39" t="n">
+        <v>47</v>
+      </c>
+      <c r="AZ39" t="n">
+        <v>47</v>
+      </c>
+      <c r="BA39" t="n">
+        <v>47</v>
+      </c>
+      <c r="BB39" t="n">
+        <v>47</v>
+      </c>
+      <c r="BC39" t="n">
+        <v>47</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>1032</v>
+        <v>1274</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>young___eagle</t>
+          <t>zKermel</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -5175,109 +7047,157 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="T40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="U40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="AC40" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="AD40" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AE40" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AF40" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AG40" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AH40" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="AI40" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="AJ40" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="AK40" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="AL40" t="n">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="AM40" t="n">
-        <v>30</v>
+        <v>53</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AV40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AW40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AX40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AY40" t="n">
+        <v>53</v>
+      </c>
+      <c r="AZ40" t="n">
+        <v>53</v>
+      </c>
+      <c r="BA40" t="n">
+        <v>53</v>
+      </c>
+      <c r="BB40" t="n">
+        <v>53</v>
+      </c>
+      <c r="BC40" t="n">
+        <v>53</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>1033</v>
+        <v>1275</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>youngguccie</t>
+          <t>zakflash</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -5329,197 +7249,293 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>0</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
+      </c>
+      <c r="V41" t="n">
+        <v>0</v>
+      </c>
+      <c r="W41" t="n">
+        <v>0</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH41" t="n">
         <v>27</v>
       </c>
-      <c r="T41" t="n">
-        <v>27</v>
-      </c>
-      <c r="U41" t="n">
-        <v>27</v>
-      </c>
-      <c r="V41" t="n">
-        <v>27</v>
-      </c>
-      <c r="W41" t="n">
-        <v>27</v>
-      </c>
-      <c r="X41" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>28</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>28</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>30</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>30</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>30</v>
-      </c>
-      <c r="AF41" t="n">
-        <v>30</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>30</v>
-      </c>
-      <c r="AH41" t="n">
-        <v>30</v>
-      </c>
       <c r="AI41" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AJ41" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="AK41" t="n">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="AL41" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="AM41" t="n">
-        <v>30</v>
+        <v>69</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>69</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>69</v>
+      </c>
+      <c r="AP41" t="n">
+        <v>69</v>
+      </c>
+      <c r="AQ41" t="n">
+        <v>69</v>
+      </c>
+      <c r="AR41" t="n">
+        <v>69</v>
+      </c>
+      <c r="AS41" t="n">
+        <v>69</v>
+      </c>
+      <c r="AT41" t="n">
+        <v>70</v>
+      </c>
+      <c r="AU41" t="n">
+        <v>70</v>
+      </c>
+      <c r="AV41" t="n">
+        <v>70</v>
+      </c>
+      <c r="AW41" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX41" t="n">
+        <v>70</v>
+      </c>
+      <c r="AY41" t="n">
+        <v>70</v>
+      </c>
+      <c r="AZ41" t="n">
+        <v>71</v>
+      </c>
+      <c r="BA41" t="n">
+        <v>71</v>
+      </c>
+      <c r="BB41" t="n">
+        <v>71</v>
+      </c>
+      <c r="BC41" t="n">
+        <v>71</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>1034</v>
+        <v>1276</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ypmx1_</t>
+          <t>zeil</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="F42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="H42" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="I42" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="J42" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="K42" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="L42" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="M42" t="n">
-        <v>61</v>
+        <v>12</v>
       </c>
       <c r="N42" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="O42" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="P42" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="Q42" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="R42" t="n">
-        <v>63</v>
+        <v>12</v>
       </c>
       <c r="S42" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="T42" t="n">
-        <v>63</v>
+        <v>13</v>
       </c>
       <c r="U42" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="V42" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="W42" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="X42" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="Y42" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="Z42" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="AA42" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="AB42" t="n">
-        <v>63</v>
+        <v>23</v>
       </c>
       <c r="AC42" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AD42" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AE42" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AF42" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AG42" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AH42" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AI42" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AJ42" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AK42" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AL42" t="n">
-        <v>65</v>
+        <v>23</v>
       </c>
       <c r="AM42" t="n">
-        <v>65</v>
+        <v>23</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT42" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AV42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AX42" t="n">
+        <v>24</v>
+      </c>
+      <c r="AY42" t="n">
+        <v>26</v>
+      </c>
+      <c r="AZ42" t="n">
+        <v>26</v>
+      </c>
+      <c r="BA42" t="n">
+        <v>26</v>
+      </c>
+      <c r="BB42" t="n">
+        <v>26</v>
+      </c>
+      <c r="BC42" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>1035</v>
+        <v>1277</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>yupbekha</t>
+          <t>zenjuryx</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -5544,103 +7560,151 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Z43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AA43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AG43" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AH43" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="AI43" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="AJ43" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="AK43" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="AL43" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="AM43" t="n">
-        <v>47</v>
+        <v>40</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AV43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AW43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY43" t="n">
+        <v>40</v>
+      </c>
+      <c r="AZ43" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA43" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB43" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC43" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>1036</v>
+        <v>1278</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>zKermel</t>
+          <t>zequifu</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -5683,206 +7747,302 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AB44" t="n">
-        <v>2</v>
+        <v>72</v>
       </c>
       <c r="AC44" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="AD44" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="AE44" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="AF44" t="n">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="AG44" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="AH44" t="n">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="AI44" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="AJ44" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="AK44" t="n">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="AL44" t="n">
-        <v>53</v>
+        <v>83</v>
       </c>
       <c r="AM44" t="n">
-        <v>53</v>
+        <v>86</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>86</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>87</v>
+      </c>
+      <c r="AP44" t="n">
+        <v>88</v>
+      </c>
+      <c r="AQ44" t="n">
+        <v>88</v>
+      </c>
+      <c r="AR44" t="n">
+        <v>89</v>
+      </c>
+      <c r="AS44" t="n">
+        <v>91</v>
+      </c>
+      <c r="AT44" t="n">
+        <v>93</v>
+      </c>
+      <c r="AU44" t="n">
+        <v>96</v>
+      </c>
+      <c r="AV44" t="n">
+        <v>96</v>
+      </c>
+      <c r="AW44" t="n">
+        <v>102</v>
+      </c>
+      <c r="AX44" t="n">
+        <v>102</v>
+      </c>
+      <c r="AY44" t="n">
+        <v>102</v>
+      </c>
+      <c r="AZ44" t="n">
+        <v>102</v>
+      </c>
+      <c r="BA44" t="n">
+        <v>102</v>
+      </c>
+      <c r="BB44" t="n">
+        <v>103</v>
+      </c>
+      <c r="BC44" t="n">
+        <v>103</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>1037</v>
+        <v>1279</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>zakflash</t>
+          <t>zerg_zerg_</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G45" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="K45" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="Z45" t="n">
-        <v>1</v>
+        <v>117</v>
       </c>
       <c r="AA45" t="n">
-        <v>1</v>
+        <v>125</v>
       </c>
       <c r="AB45" t="n">
-        <v>3</v>
+        <v>125</v>
       </c>
       <c r="AC45" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="AD45" t="n">
-        <v>5</v>
+        <v>125</v>
       </c>
       <c r="AE45" t="n">
-        <v>6</v>
+        <v>125</v>
       </c>
       <c r="AF45" t="n">
-        <v>7</v>
+        <v>125</v>
       </c>
       <c r="AG45" t="n">
-        <v>22</v>
+        <v>125</v>
       </c>
       <c r="AH45" t="n">
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="AI45" t="n">
-        <v>32</v>
+        <v>129</v>
       </c>
       <c r="AJ45" t="n">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="AK45" t="n">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="AL45" t="n">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="AM45" t="n">
-        <v>69</v>
+        <v>129</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AP45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AQ45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AR45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AS45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AT45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AU45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AV45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AW45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AX45" t="n">
+        <v>129</v>
+      </c>
+      <c r="AY45" t="n">
+        <v>131</v>
+      </c>
+      <c r="AZ45" t="n">
+        <v>133</v>
+      </c>
+      <c r="BA45" t="n">
+        <v>133</v>
+      </c>
+      <c r="BB45" t="n">
+        <v>136</v>
+      </c>
+      <c r="BC45" t="n">
+        <v>136</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>1038</v>
+        <v>1280</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>zenjuryx</t>
+          <t>ziico13</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -5907,103 +8067,151 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="P46" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q46" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R46" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="S46" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="T46" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="U46" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="V46" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="W46" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="X46" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="Y46" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="Z46" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="AA46" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AB46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AC46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AD46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AE46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AF46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AG46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AH46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AI46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AJ46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AK46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AL46" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="AM46" t="n">
-        <v>40</v>
+        <v>31</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>31</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>31</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>31</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>31</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>1039</v>
+        <v>1281</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>zequifu</t>
+          <t>zmaauu</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -6013,239 +8221,335 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="V47" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="W47" t="n">
-        <v>36</v>
+        <v>17</v>
       </c>
       <c r="X47" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="Y47" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="Z47" t="n">
-        <v>51</v>
+        <v>18</v>
       </c>
       <c r="AA47" t="n">
-        <v>62</v>
+        <v>18</v>
       </c>
       <c r="AB47" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="AC47" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="AD47" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="AE47" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="AF47" t="n">
-        <v>72</v>
+        <v>18</v>
       </c>
       <c r="AG47" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="AH47" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="AI47" t="n">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="AJ47" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="AK47" t="n">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="AL47" t="n">
-        <v>83</v>
+        <v>18</v>
       </c>
       <c r="AM47" t="n">
-        <v>86</v>
+        <v>18</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>39</v>
+      </c>
+      <c r="AP47" t="n">
+        <v>43</v>
+      </c>
+      <c r="AQ47" t="n">
+        <v>44</v>
+      </c>
+      <c r="AR47" t="n">
+        <v>44</v>
+      </c>
+      <c r="AS47" t="n">
+        <v>45</v>
+      </c>
+      <c r="AT47" t="n">
+        <v>45</v>
+      </c>
+      <c r="AU47" t="n">
+        <v>45</v>
+      </c>
+      <c r="AV47" t="n">
+        <v>45</v>
+      </c>
+      <c r="AW47" t="n">
+        <v>45</v>
+      </c>
+      <c r="AX47" t="n">
+        <v>45</v>
+      </c>
+      <c r="AY47" t="n">
+        <v>45</v>
+      </c>
+      <c r="AZ47" t="n">
+        <v>45</v>
+      </c>
+      <c r="BA47" t="n">
+        <v>45</v>
+      </c>
+      <c r="BB47" t="n">
+        <v>45</v>
+      </c>
+      <c r="BC47" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>1040</v>
+        <v>1282</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>zerg_zerg_</t>
+          <t>zoffeswe</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G48" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="N48" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
-        <v>52</v>
+        <v>4</v>
       </c>
       <c r="Q48" t="n">
-        <v>76</v>
+        <v>14</v>
       </c>
       <c r="R48" t="n">
-        <v>76</v>
+        <v>47</v>
       </c>
       <c r="S48" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="T48" t="n">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="U48" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="V48" t="n">
-        <v>77</v>
+        <v>54</v>
       </c>
       <c r="W48" t="n">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="X48" t="n">
-        <v>87</v>
+        <v>61</v>
       </c>
       <c r="Y48" t="n">
-        <v>117</v>
+        <v>62</v>
       </c>
       <c r="Z48" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="AA48" t="n">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="AB48" t="n">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="AC48" t="n">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="AD48" t="n">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="AE48" t="n">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="AF48" t="n">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="AG48" t="n">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c r="AH48" t="n">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="AI48" t="n">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="AJ48" t="n">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="AK48" t="n">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="AL48" t="n">
-        <v>129</v>
+        <v>68</v>
       </c>
       <c r="AM48" t="n">
-        <v>129</v>
+        <v>68</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AP48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AQ48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AR48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AS48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AT48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AU48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AV48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AW48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AX48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AY48" t="n">
+        <v>68</v>
+      </c>
+      <c r="AZ48" t="n">
+        <v>68</v>
+      </c>
+      <c r="BA48" t="n">
+        <v>68</v>
+      </c>
+      <c r="BB48" t="n">
+        <v>68</v>
+      </c>
+      <c r="BC48" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>1041</v>
+        <v>1283</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ziico13</t>
+          <t>zoro_enma1</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -6282,91 +8586,139 @@
         <v>0</v>
       </c>
       <c r="N49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="O49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AE49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AF49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AL49" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>31</v>
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV49" t="n">
+        <v>93</v>
+      </c>
+      <c r="AW49" t="n">
+        <v>96</v>
+      </c>
+      <c r="AX49" t="n">
+        <v>114</v>
+      </c>
+      <c r="AY49" t="n">
+        <v>127</v>
+      </c>
+      <c r="AZ49" t="n">
+        <v>128</v>
+      </c>
+      <c r="BA49" t="n">
+        <v>129</v>
+      </c>
+      <c r="BB49" t="n">
+        <v>134</v>
+      </c>
+      <c r="BC49" t="n">
+        <v>134</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>1042</v>
+        <v>1284</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>zoffeswe</t>
+          <t>zuccaaa</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -6388,106 +8740,154 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="O50" t="n">
-        <v>3</v>
+        <v>144</v>
       </c>
       <c r="P50" t="n">
-        <v>4</v>
+        <v>144</v>
       </c>
       <c r="Q50" t="n">
-        <v>14</v>
+        <v>144</v>
       </c>
       <c r="R50" t="n">
-        <v>47</v>
+        <v>144</v>
       </c>
       <c r="S50" t="n">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="T50" t="n">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="U50" t="n">
-        <v>53</v>
+        <v>147</v>
       </c>
       <c r="V50" t="n">
-        <v>54</v>
+        <v>147</v>
       </c>
       <c r="W50" t="n">
-        <v>60</v>
+        <v>147</v>
       </c>
       <c r="X50" t="n">
-        <v>61</v>
+        <v>154</v>
       </c>
       <c r="Y50" t="n">
-        <v>62</v>
+        <v>157</v>
       </c>
       <c r="Z50" t="n">
-        <v>68</v>
+        <v>174</v>
       </c>
       <c r="AA50" t="n">
-        <v>68</v>
+        <v>174</v>
       </c>
       <c r="AB50" t="n">
-        <v>68</v>
+        <v>194</v>
       </c>
       <c r="AC50" t="n">
-        <v>68</v>
+        <v>214</v>
       </c>
       <c r="AD50" t="n">
-        <v>68</v>
+        <v>215</v>
       </c>
       <c r="AE50" t="n">
-        <v>68</v>
+        <v>219</v>
       </c>
       <c r="AF50" t="n">
-        <v>68</v>
+        <v>225</v>
       </c>
       <c r="AG50" t="n">
-        <v>68</v>
+        <v>229</v>
       </c>
       <c r="AH50" t="n">
-        <v>68</v>
+        <v>229</v>
       </c>
       <c r="AI50" t="n">
-        <v>68</v>
+        <v>230</v>
       </c>
       <c r="AJ50" t="n">
-        <v>68</v>
+        <v>232</v>
       </c>
       <c r="AK50" t="n">
-        <v>68</v>
+        <v>232</v>
       </c>
       <c r="AL50" t="n">
-        <v>68</v>
+        <v>233</v>
       </c>
       <c r="AM50" t="n">
-        <v>68</v>
+        <v>234</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>234</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>237</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>237</v>
+      </c>
+      <c r="AQ50" t="n">
+        <v>237</v>
+      </c>
+      <c r="AR50" t="n">
+        <v>245</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>245</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>245</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>245</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>248</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>248</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>248</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>248</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>248</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>248</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>248</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>248</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>1043</v>
+        <v>1285</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>zuccaaa</t>
+          <t>zwiebelbrotlive</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -6509,102 +8909,150 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="J51" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="K51" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="L51" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="M51" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="O51" t="n">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="P51" t="n">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="R51" t="n">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="S51" t="n">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="T51" t="n">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="U51" t="n">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="V51" t="n">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="W51" t="n">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="X51" t="n">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="Y51" t="n">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="Z51" t="n">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="AA51" t="n">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="AB51" t="n">
-        <v>194</v>
+        <v>13</v>
       </c>
       <c r="AC51" t="n">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="AD51" t="n">
-        <v>215</v>
+        <v>13</v>
       </c>
       <c r="AE51" t="n">
-        <v>219</v>
+        <v>13</v>
       </c>
       <c r="AF51" t="n">
-        <v>225</v>
+        <v>13</v>
       </c>
       <c r="AG51" t="n">
-        <v>229</v>
+        <v>13</v>
       </c>
       <c r="AH51" t="n">
-        <v>229</v>
+        <v>13</v>
       </c>
       <c r="AI51" t="n">
-        <v>230</v>
+        <v>13</v>
       </c>
       <c r="AJ51" t="n">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="AK51" t="n">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="AL51" t="n">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="AM51" t="n">
-        <v>234</v>
+        <v>13</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AP51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AQ51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AR51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AS51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>27</v>
+      </c>
+      <c r="BA51" t="n">
+        <v>27</v>
+      </c>
+      <c r="BB51" t="n">
+        <v>28</v>
+      </c>
+      <c r="BC51" t="n">
+        <v>29</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>1044</v>
+        <v>1286</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -6722,489 +9170,898 @@
       <c r="AM52" t="n">
         <v>55</v>
       </c>
+      <c r="AN52" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>59</v>
+      </c>
+      <c r="AP52" t="n">
+        <v>65</v>
+      </c>
+      <c r="AQ52" t="n">
+        <v>65</v>
+      </c>
+      <c r="AR52" t="n">
+        <v>65</v>
+      </c>
+      <c r="AS52" t="n">
+        <v>65</v>
+      </c>
+      <c r="AT52" t="n">
+        <v>71</v>
+      </c>
+      <c r="AU52" t="n">
+        <v>71</v>
+      </c>
+      <c r="AV52" t="n">
+        <v>72</v>
+      </c>
+      <c r="AW52" t="n">
+        <v>73</v>
+      </c>
+      <c r="AX52" t="n">
+        <v>73</v>
+      </c>
+      <c r="AY52" t="n">
+        <v>74</v>
+      </c>
+      <c r="AZ52" t="n">
+        <v>77</v>
+      </c>
+      <c r="BA52" t="n">
+        <v>78</v>
+      </c>
+      <c r="BB52" t="n">
+        <v>79</v>
+      </c>
+      <c r="BC52" t="n">
+        <v>79</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>1045</v>
+        <v>1287</v>
       </c>
       <c r="B53" t="inlineStr">
+        <is>
+          <t>zylandpepstein</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>143</v>
+      </c>
+      <c r="AU53" t="n">
+        <v>154</v>
+      </c>
+      <c r="AV53" t="n">
+        <v>154</v>
+      </c>
+      <c r="AW53" t="n">
+        <v>154</v>
+      </c>
+      <c r="AX53" t="n">
+        <v>154</v>
+      </c>
+      <c r="AY53" t="n">
+        <v>154</v>
+      </c>
+      <c r="AZ53" t="n">
+        <v>154</v>
+      </c>
+      <c r="BA53" t="n">
+        <v>154</v>
+      </c>
+      <c r="BB53" t="n">
+        <v>154</v>
+      </c>
+      <c r="BC53" t="n">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>1288</v>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>محمدحسين</t>
         </is>
       </c>
-      <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="n">
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
         <v>39</v>
       </c>
-      <c r="E53" t="n">
+      <c r="E54" t="n">
         <v>39</v>
       </c>
-      <c r="F53" t="n">
+      <c r="F54" t="n">
         <v>39</v>
       </c>
-      <c r="G53" t="n">
+      <c r="G54" t="n">
         <v>39</v>
       </c>
-      <c r="H53" t="n">
+      <c r="H54" t="n">
         <v>39</v>
       </c>
-      <c r="I53" t="n">
+      <c r="I54" t="n">
         <v>39</v>
       </c>
-      <c r="J53" t="n">
+      <c r="J54" t="n">
         <v>39</v>
       </c>
-      <c r="K53" t="n">
+      <c r="K54" t="n">
         <v>39</v>
       </c>
-      <c r="L53" t="n">
+      <c r="L54" t="n">
         <v>39</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M54" t="n">
         <v>39</v>
       </c>
-      <c r="N53" t="n">
+      <c r="N54" t="n">
         <v>39</v>
       </c>
-      <c r="O53" t="n">
+      <c r="O54" t="n">
         <v>39</v>
       </c>
-      <c r="P53" t="n">
+      <c r="P54" t="n">
         <v>39</v>
       </c>
-      <c r="Q53" t="n">
+      <c r="Q54" t="n">
         <v>39</v>
       </c>
-      <c r="R53" t="n">
+      <c r="R54" t="n">
         <v>39</v>
       </c>
-      <c r="S53" t="n">
+      <c r="S54" t="n">
         <v>39</v>
       </c>
-      <c r="T53" t="n">
+      <c r="T54" t="n">
         <v>39</v>
       </c>
-      <c r="U53" t="n">
+      <c r="U54" t="n">
         <v>39</v>
       </c>
-      <c r="V53" t="n">
+      <c r="V54" t="n">
         <v>39</v>
       </c>
-      <c r="W53" t="n">
+      <c r="W54" t="n">
         <v>39</v>
       </c>
-      <c r="X53" t="n">
+      <c r="X54" t="n">
         <v>39</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Y54" t="n">
         <v>39</v>
       </c>
-      <c r="Z53" t="n">
+      <c r="Z54" t="n">
         <v>39</v>
       </c>
-      <c r="AA53" t="n">
+      <c r="AA54" t="n">
         <v>39</v>
       </c>
-      <c r="AB53" t="n">
+      <c r="AB54" t="n">
         <v>39</v>
       </c>
-      <c r="AC53" t="n">
+      <c r="AC54" t="n">
         <v>40</v>
       </c>
-      <c r="AD53" t="n">
+      <c r="AD54" t="n">
         <v>40</v>
       </c>
-      <c r="AE53" t="n">
+      <c r="AE54" t="n">
         <v>40</v>
       </c>
-      <c r="AF53" t="n">
+      <c r="AF54" t="n">
         <v>40</v>
       </c>
-      <c r="AG53" t="n">
+      <c r="AG54" t="n">
         <v>40</v>
       </c>
-      <c r="AH53" t="n">
+      <c r="AH54" t="n">
         <v>40</v>
       </c>
-      <c r="AI53" t="n">
+      <c r="AI54" t="n">
         <v>40</v>
       </c>
-      <c r="AJ53" t="n">
+      <c r="AJ54" t="n">
         <v>40</v>
       </c>
-      <c r="AK53" t="n">
+      <c r="AK54" t="n">
         <v>40</v>
       </c>
-      <c r="AL53" t="n">
+      <c r="AL54" t="n">
         <v>40</v>
       </c>
-      <c r="AM53" t="n">
+      <c r="AM54" t="n">
         <v>40</v>
       </c>
+      <c r="AN54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>40</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>40</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>40</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>40</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>40</v>
+      </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="n">
-        <v>1046</v>
-      </c>
-      <c r="B54" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>1289</v>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>金龙</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" t="n">
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" t="n">
         <v>1</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G55" t="n">
         <v>1</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H55" t="n">
         <v>11</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>20</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>20</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K55" t="n">
         <v>21</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L55" t="n">
         <v>21</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M55" t="n">
         <v>21</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N55" t="n">
         <v>21</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O55" t="n">
         <v>21</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P55" t="n">
         <v>21</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q55" t="n">
         <v>21</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R55" t="n">
         <v>21</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S55" t="n">
         <v>21</v>
       </c>
-      <c r="T54" t="n">
+      <c r="T55" t="n">
         <v>21</v>
       </c>
-      <c r="U54" t="n">
+      <c r="U55" t="n">
         <v>21</v>
       </c>
-      <c r="V54" t="n">
+      <c r="V55" t="n">
         <v>21</v>
       </c>
-      <c r="W54" t="n">
+      <c r="W55" t="n">
         <v>21</v>
       </c>
-      <c r="X54" t="n">
+      <c r="X55" t="n">
         <v>22</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Y55" t="n">
         <v>23</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="Z55" t="n">
         <v>24</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AA55" t="n">
         <v>25</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AB55" t="n">
         <v>26</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AC55" t="n">
         <v>27</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AD55" t="n">
         <v>27</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AE55" t="n">
         <v>27</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AF55" t="n">
         <v>27</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AG55" t="n">
         <v>28</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH55" t="n">
         <v>28</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AI55" t="n">
         <v>28</v>
       </c>
-      <c r="AJ54" t="n">
+      <c r="AJ55" t="n">
         <v>31</v>
       </c>
-      <c r="AK54" t="n">
+      <c r="AK55" t="n">
         <v>31</v>
       </c>
-      <c r="AL54" t="n">
+      <c r="AL55" t="n">
         <v>31</v>
       </c>
-      <c r="AM54" t="n">
+      <c r="AM55" t="n">
         <v>31</v>
       </c>
+      <c r="AN55" t="n">
+        <v>31</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>31</v>
+      </c>
+      <c r="AP55" t="n">
+        <v>31</v>
+      </c>
+      <c r="AQ55" t="n">
+        <v>38</v>
+      </c>
+      <c r="AR55" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS55" t="n">
+        <v>39</v>
+      </c>
+      <c r="AT55" t="n">
+        <v>40</v>
+      </c>
+      <c r="AU55" t="n">
+        <v>40</v>
+      </c>
+      <c r="AV55" t="n">
+        <v>40</v>
+      </c>
+      <c r="AW55" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX55" t="n">
+        <v>40</v>
+      </c>
+      <c r="AY55" t="n">
+        <v>56</v>
+      </c>
+      <c r="AZ55" t="n">
+        <v>60</v>
+      </c>
+      <c r="BA55" t="n">
+        <v>60</v>
+      </c>
+      <c r="BB55" t="n">
+        <v>61</v>
+      </c>
+      <c r="BC55" t="n">
+        <v>62</v>
+      </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>1047</v>
-      </c>
-      <c r="B55" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>1290</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>빵댕이ㅋ</t>
         </is>
       </c>
-      <c r="C55" t="n">
+      <c r="C56" t="n">
         <v>2</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D56" t="n">
         <v>7</v>
       </c>
-      <c r="E55" t="n">
+      <c r="E56" t="n">
         <v>7</v>
       </c>
-      <c r="F55" t="n">
+      <c r="F56" t="n">
         <v>9</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G56" t="n">
         <v>10</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H56" t="n">
         <v>12</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I56" t="n">
         <v>15</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J56" t="n">
         <v>17</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K56" t="n">
         <v>18</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L56" t="n">
         <v>18</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M56" t="n">
         <v>20</v>
       </c>
-      <c r="N55" t="n">
+      <c r="N56" t="n">
         <v>21</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O56" t="n">
         <v>21</v>
       </c>
-      <c r="P55" t="n">
+      <c r="P56" t="n">
         <v>22</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="Q56" t="n">
         <v>22</v>
       </c>
-      <c r="R55" t="n">
+      <c r="R56" t="n">
         <v>24</v>
       </c>
-      <c r="S55" t="n">
+      <c r="S56" t="n">
         <v>28</v>
       </c>
-      <c r="T55" t="n">
+      <c r="T56" t="n">
         <v>29</v>
       </c>
-      <c r="U55" t="n">
+      <c r="U56" t="n">
         <v>30</v>
       </c>
-      <c r="V55" t="n">
+      <c r="V56" t="n">
         <v>31</v>
       </c>
-      <c r="W55" t="n">
+      <c r="W56" t="n">
         <v>31</v>
       </c>
-      <c r="X55" t="n">
+      <c r="X56" t="n">
         <v>32</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Y56" t="n">
         <v>33</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="Z56" t="n">
         <v>33</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AA56" t="n">
         <v>33</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AB56" t="n">
         <v>34</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AC56" t="n">
         <v>35</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AD56" t="n">
         <v>37</v>
       </c>
-      <c r="AE55" t="n">
+      <c r="AE56" t="n">
         <v>37</v>
       </c>
-      <c r="AF55" t="n">
+      <c r="AF56" t="n">
         <v>37</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AG56" t="n">
         <v>37</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AH56" t="n">
         <v>37</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AI56" t="n">
         <v>37</v>
       </c>
-      <c r="AJ55" t="n">
+      <c r="AJ56" t="n">
         <v>38</v>
       </c>
-      <c r="AK55" t="n">
+      <c r="AK56" t="n">
         <v>38</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AL56" t="n">
         <v>38</v>
       </c>
-      <c r="AM55" t="n">
+      <c r="AM56" t="n">
         <v>38</v>
       </c>
+      <c r="AN56" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP56" t="n">
+        <v>39</v>
+      </c>
+      <c r="AQ56" t="n">
+        <v>39</v>
+      </c>
+      <c r="AR56" t="n">
+        <v>40</v>
+      </c>
+      <c r="AS56" t="n">
+        <v>43</v>
+      </c>
+      <c r="AT56" t="n">
+        <v>44</v>
+      </c>
+      <c r="AU56" t="n">
+        <v>45</v>
+      </c>
+      <c r="AV56" t="n">
+        <v>47</v>
+      </c>
+      <c r="AW56" t="n">
+        <v>47</v>
+      </c>
+      <c r="AX56" t="n">
+        <v>48</v>
+      </c>
+      <c r="AY56" t="n">
+        <v>48</v>
+      </c>
+      <c r="AZ56" t="n">
+        <v>49</v>
+      </c>
+      <c r="BA56" t="n">
+        <v>49</v>
+      </c>
+      <c r="BB56" t="n">
+        <v>49</v>
+      </c>
+      <c r="BC56" t="n">
+        <v>49</v>
+      </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>1048</v>
-      </c>
-      <c r="B56" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>1291</v>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>알래스카해달</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C57" t="n">
         <v>95</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D57" t="n">
         <v>95</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E57" t="n">
         <v>95</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F57" t="n">
         <v>193</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G57" t="n">
         <v>193</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H57" t="n">
         <v>272</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I57" t="n">
         <v>274</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J57" t="n">
         <v>274</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K57" t="n">
         <v>302</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L57" t="n">
         <v>358</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M57" t="n">
         <v>426</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N57" t="n">
         <v>426</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O57" t="n">
         <v>426</v>
       </c>
-      <c r="P56" t="n">
+      <c r="P57" t="n">
         <v>436</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q57" t="n">
         <v>478</v>
       </c>
-      <c r="R56" t="n">
+      <c r="R57" t="n">
         <v>584</v>
       </c>
-      <c r="S56" t="n">
+      <c r="S57" t="n">
         <v>623</v>
       </c>
-      <c r="T56" t="n">
+      <c r="T57" t="n">
         <v>661</v>
       </c>
-      <c r="U56" t="n">
+      <c r="U57" t="n">
         <v>685</v>
       </c>
-      <c r="V56" t="n">
+      <c r="V57" t="n">
         <v>685</v>
       </c>
-      <c r="W56" t="n">
+      <c r="W57" t="n">
         <v>685</v>
       </c>
-      <c r="X56" t="n">
+      <c r="X57" t="n">
         <v>761</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Y57" t="n">
         <v>857</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="Z57" t="n">
         <v>879</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AA57" t="n">
         <v>981</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AB57" t="n">
         <v>981</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AC57" t="n">
         <v>1041</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AD57" t="n">
         <v>1041</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AE57" t="n">
         <v>1151</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AF57" t="n">
         <v>1164</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AG57" t="n">
         <v>1191</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AH57" t="n">
         <v>1202</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AI57" t="n">
         <v>1202</v>
       </c>
-      <c r="AJ56" t="n">
+      <c r="AJ57" t="n">
         <v>1202</v>
       </c>
-      <c r="AK56" t="n">
+      <c r="AK57" t="n">
         <v>1230</v>
       </c>
-      <c r="AL56" t="n">
+      <c r="AL57" t="n">
         <v>1282</v>
       </c>
-      <c r="AM56" t="n">
+      <c r="AM57" t="n">
         <v>1313</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>1313</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AP57" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AQ57" t="n">
+        <v>1330</v>
+      </c>
+      <c r="AR57" t="n">
+        <v>1399</v>
+      </c>
+      <c r="AS57" t="n">
+        <v>1399</v>
+      </c>
+      <c r="AT57" t="n">
+        <v>1401</v>
+      </c>
+      <c r="AU57" t="n">
+        <v>1401</v>
+      </c>
+      <c r="AV57" t="n">
+        <v>1401</v>
+      </c>
+      <c r="AW57" t="n">
+        <v>1401</v>
+      </c>
+      <c r="AX57" t="n">
+        <v>1420</v>
+      </c>
+      <c r="AY57" t="n">
+        <v>1420</v>
+      </c>
+      <c r="AZ57" t="n">
+        <v>1422</v>
+      </c>
+      <c r="BA57" t="n">
+        <v>1454</v>
+      </c>
+      <c r="BB57" t="n">
+        <v>1482</v>
+      </c>
+      <c r="BC57" t="n">
+        <v>1482</v>
       </c>
     </row>
   </sheetData>

--- a/barRace/chattersRace2026.xlsx
+++ b/barRace/chattersRace2026.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC57"/>
+  <dimension ref="A1:BT58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -599,10 +599,61 @@
       <c r="BC1" s="2" t="n">
         <v>46090</v>
       </c>
+      <c r="BD1" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="BE1" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="BF1" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="BG1" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="BH1" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="BI1" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="BJ1" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="BK1" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="BL1" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="BM1" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="BN1" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="BO1" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="BP1" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="BQ1" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="BR1" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="BS1" s="2" t="n">
+        <v>46110</v>
+      </c>
+      <c r="BT1" s="2" t="n">
+        <v>46112</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -768,10 +819,61 @@
       <c r="BC2" t="n">
         <v>2955</v>
       </c>
+      <c r="BD2" t="n">
+        <v>3009</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>3037</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>3061</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3142</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>3230</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3336</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>3423</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>3481</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>3599</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>3676</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>3778</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>3841</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>3911</v>
+      </c>
+      <c r="BQ2" t="n">
+        <v>4038</v>
+      </c>
+      <c r="BR2" t="n">
+        <v>4083</v>
+      </c>
+      <c r="BS2" t="n">
+        <v>4161</v>
+      </c>
+      <c r="BT2" t="n">
+        <v>4221</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -937,10 +1039,61 @@
       <c r="BC3" t="n">
         <v>162</v>
       </c>
+      <c r="BD3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BQ3" t="n">
+        <v>162</v>
+      </c>
+      <c r="BR3" t="n">
+        <v>175</v>
+      </c>
+      <c r="BS3" t="n">
+        <v>175</v>
+      </c>
+      <c r="BT3" t="n">
+        <v>201</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -1106,10 +1259,61 @@
       <c r="BC4" t="n">
         <v>4716</v>
       </c>
+      <c r="BD4" t="n">
+        <v>4716</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>4716</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>4716</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>4716</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>4716</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>4764</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>4764</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>4764</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>4764</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>4764</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>4764</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>4769</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>4769</v>
+      </c>
+      <c r="BQ4" t="n">
+        <v>4769</v>
+      </c>
+      <c r="BR4" t="n">
+        <v>4771</v>
+      </c>
+      <c r="BS4" t="n">
+        <v>4771</v>
+      </c>
+      <c r="BT4" t="n">
+        <v>4771</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -1275,10 +1479,61 @@
       <c r="BC5" t="n">
         <v>4307</v>
       </c>
+      <c r="BD5" t="n">
+        <v>4410</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>4483</v>
+      </c>
+      <c r="BF5" t="n">
+        <v>4561</v>
+      </c>
+      <c r="BG5" t="n">
+        <v>4602</v>
+      </c>
+      <c r="BH5" t="n">
+        <v>4631</v>
+      </c>
+      <c r="BI5" t="n">
+        <v>4667</v>
+      </c>
+      <c r="BJ5" t="n">
+        <v>4678</v>
+      </c>
+      <c r="BK5" t="n">
+        <v>4678</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>4705</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>4766</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>4809</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>4837</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>4907</v>
+      </c>
+      <c r="BQ5" t="n">
+        <v>5018</v>
+      </c>
+      <c r="BR5" t="n">
+        <v>5125</v>
+      </c>
+      <c r="BS5" t="n">
+        <v>5187</v>
+      </c>
+      <c r="BT5" t="n">
+        <v>5237</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>143</v>
+        <v>193</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1444,10 +1699,61 @@
       <c r="BC6" t="n">
         <v>12769</v>
       </c>
+      <c r="BD6" t="n">
+        <v>13288</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>13687</v>
+      </c>
+      <c r="BF6" t="n">
+        <v>14003</v>
+      </c>
+      <c r="BG6" t="n">
+        <v>14462</v>
+      </c>
+      <c r="BH6" t="n">
+        <v>14884</v>
+      </c>
+      <c r="BI6" t="n">
+        <v>15261</v>
+      </c>
+      <c r="BJ6" t="n">
+        <v>15821</v>
+      </c>
+      <c r="BK6" t="n">
+        <v>16380</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>16744</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>17282</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>18158</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>18656</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>19023</v>
+      </c>
+      <c r="BQ6" t="n">
+        <v>19571</v>
+      </c>
+      <c r="BR6" t="n">
+        <v>20745</v>
+      </c>
+      <c r="BS6" t="n">
+        <v>21296</v>
+      </c>
+      <c r="BT6" t="n">
+        <v>21686</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>145</v>
+        <v>197</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1613,10 +1919,61 @@
       <c r="BC7" t="n">
         <v>3487</v>
       </c>
+      <c r="BD7" t="n">
+        <v>3651</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>3828</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>3913</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>4114</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>4324</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>4396</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>4396</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>4484</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>4608</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>4792</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>4988</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>5002</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>5135</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>5458</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>5458</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>5494</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>5494</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>177</v>
+        <v>236</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1782,10 +2139,61 @@
       <c r="BC8" t="n">
         <v>13156</v>
       </c>
+      <c r="BD8" t="n">
+        <v>13156</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>13239</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>13239</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>13579</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>13665</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>13978</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>14254</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>14574</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>14831</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>15134</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>15134</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>15134</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>15309</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>15309</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>15633</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>15910</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>15910</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>197</v>
+        <v>260</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1951,10 +2359,61 @@
       <c r="BC9" t="n">
         <v>1134</v>
       </c>
+      <c r="BD9" t="n">
+        <v>1157</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1157</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>1269</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>1291</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>1335</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>1372</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>1378</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>1418</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1446</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1447</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>1447</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>1447</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>1448</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>1468</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>1470</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>1472</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>1497</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>201</v>
+        <v>264</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -2120,10 +2579,61 @@
       <c r="BC10" t="n">
         <v>7180</v>
       </c>
+      <c r="BD10" t="n">
+        <v>7384</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>7564</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>7769</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>7896</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>8017</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>8152</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>8192</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>8220</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>8265</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>8551</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>8686</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>8810</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>8976</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>9110</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>9313</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>9396</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>9396</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>209</v>
+        <v>273</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2289,10 +2799,61 @@
       <c r="BC11" t="n">
         <v>4554</v>
       </c>
+      <c r="BD11" t="n">
+        <v>4648</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>4735</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>4859</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>4924</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>5026</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>5126</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>5197</v>
+      </c>
+      <c r="BK11" t="n">
+        <v>5353</v>
+      </c>
+      <c r="BL11" t="n">
+        <v>5482</v>
+      </c>
+      <c r="BM11" t="n">
+        <v>5552</v>
+      </c>
+      <c r="BN11" t="n">
+        <v>5679</v>
+      </c>
+      <c r="BO11" t="n">
+        <v>5726</v>
+      </c>
+      <c r="BP11" t="n">
+        <v>5758</v>
+      </c>
+      <c r="BQ11" t="n">
+        <v>6039</v>
+      </c>
+      <c r="BR11" t="n">
+        <v>6114</v>
+      </c>
+      <c r="BS11" t="n">
+        <v>6155</v>
+      </c>
+      <c r="BT11" t="n">
+        <v>6283</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>210</v>
+        <v>274</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -2458,10 +3019,61 @@
       <c r="BC12" t="n">
         <v>18480</v>
       </c>
+      <c r="BD12" t="n">
+        <v>18786</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>19067</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>19478</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>19735</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>19899</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>20248</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>20459</v>
+      </c>
+      <c r="BK12" t="n">
+        <v>20849</v>
+      </c>
+      <c r="BL12" t="n">
+        <v>21101</v>
+      </c>
+      <c r="BM12" t="n">
+        <v>21643</v>
+      </c>
+      <c r="BN12" t="n">
+        <v>21989</v>
+      </c>
+      <c r="BO12" t="n">
+        <v>22244</v>
+      </c>
+      <c r="BP12" t="n">
+        <v>22499</v>
+      </c>
+      <c r="BQ12" t="n">
+        <v>22839</v>
+      </c>
+      <c r="BR12" t="n">
+        <v>23462</v>
+      </c>
+      <c r="BS12" t="n">
+        <v>23804</v>
+      </c>
+      <c r="BT12" t="n">
+        <v>24171</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>224</v>
+        <v>296</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2627,10 +3239,61 @@
       <c r="BC13" t="n">
         <v>4606</v>
       </c>
+      <c r="BD13" t="n">
+        <v>4662</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>4743</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>4858</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>4937</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>5021</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>5191</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>5328</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>5531</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>5655</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>5734</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>5860</v>
+      </c>
+      <c r="BO13" t="n">
+        <v>5926</v>
+      </c>
+      <c r="BP13" t="n">
+        <v>5970</v>
+      </c>
+      <c r="BQ13" t="n">
+        <v>6055</v>
+      </c>
+      <c r="BR13" t="n">
+        <v>6206</v>
+      </c>
+      <c r="BS13" t="n">
+        <v>6251</v>
+      </c>
+      <c r="BT13" t="n">
+        <v>6262</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>292</v>
+        <v>387</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2796,10 +3459,61 @@
       <c r="BC14" t="n">
         <v>9127</v>
       </c>
+      <c r="BD14" t="n">
+        <v>9249</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>9370</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>9538</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>9538</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>9538</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>9538</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>10024</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>10222</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>10222</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>10316</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>10783</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>10783</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>11090</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>11192</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>11412</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>11696</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>11839</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>311</v>
+        <v>407</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2965,10 +3679,61 @@
       <c r="BC15" t="n">
         <v>12278</v>
       </c>
+      <c r="BD15" t="n">
+        <v>12494</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>12602</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>12831</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>12987</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>13019</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>13151</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>13436</v>
+      </c>
+      <c r="BK15" t="n">
+        <v>13605</v>
+      </c>
+      <c r="BL15" t="n">
+        <v>13633</v>
+      </c>
+      <c r="BM15" t="n">
+        <v>13837</v>
+      </c>
+      <c r="BN15" t="n">
+        <v>14198</v>
+      </c>
+      <c r="BO15" t="n">
+        <v>14361</v>
+      </c>
+      <c r="BP15" t="n">
+        <v>14450</v>
+      </c>
+      <c r="BQ15" t="n">
+        <v>14528</v>
+      </c>
+      <c r="BR15" t="n">
+        <v>15026</v>
+      </c>
+      <c r="BS15" t="n">
+        <v>15026</v>
+      </c>
+      <c r="BT15" t="n">
+        <v>15070</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>316</v>
+        <v>414</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -3134,10 +3899,61 @@
       <c r="BC16" t="n">
         <v>4298</v>
       </c>
+      <c r="BD16" t="n">
+        <v>4334</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4378</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>4411</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>4411</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>4411</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>4411</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>4420</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>4420</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>4420</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>4420</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>4432</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>4432</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>4432</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>4438</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>4438</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>4438</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>4438</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>321</v>
+        <v>420</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -3303,10 +4119,61 @@
       <c r="BC17" t="n">
         <v>1692</v>
       </c>
+      <c r="BD17" t="n">
+        <v>1694</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1694</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>1694</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>1694</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>1694</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>1694</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>1698</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>1698</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>1698</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>1698</v>
+      </c>
+      <c r="BN17" t="n">
+        <v>1759</v>
+      </c>
+      <c r="BO17" t="n">
+        <v>1759</v>
+      </c>
+      <c r="BP17" t="n">
+        <v>1759</v>
+      </c>
+      <c r="BQ17" t="n">
+        <v>1759</v>
+      </c>
+      <c r="BR17" t="n">
+        <v>1785</v>
+      </c>
+      <c r="BS17" t="n">
+        <v>1785</v>
+      </c>
+      <c r="BT17" t="n">
+        <v>1788</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>359</v>
+        <v>469</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -3472,10 +4339,61 @@
       <c r="BC18" t="n">
         <v>2331</v>
       </c>
+      <c r="BD18" t="n">
+        <v>2331</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>2331</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>2331</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2331</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>2331</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2331</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>2339</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>2356</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>2362</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>2362</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>2362</v>
+      </c>
+      <c r="BO18" t="n">
+        <v>2362</v>
+      </c>
+      <c r="BP18" t="n">
+        <v>2362</v>
+      </c>
+      <c r="BQ18" t="n">
+        <v>2362</v>
+      </c>
+      <c r="BR18" t="n">
+        <v>2362</v>
+      </c>
+      <c r="BS18" t="n">
+        <v>2362</v>
+      </c>
+      <c r="BT18" t="n">
+        <v>2385</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>393</v>
+        <v>515</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -3641,10 +4559,61 @@
       <c r="BC19" t="n">
         <v>9770</v>
       </c>
+      <c r="BD19" t="n">
+        <v>9991</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>10071</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>10139</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>10185</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>10317</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>10526</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>10693</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>10830</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>11054</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>11061</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>11328</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>11347</v>
+      </c>
+      <c r="BP19" t="n">
+        <v>11363</v>
+      </c>
+      <c r="BQ19" t="n">
+        <v>11363</v>
+      </c>
+      <c r="BR19" t="n">
+        <v>11445</v>
+      </c>
+      <c r="BS19" t="n">
+        <v>11674</v>
+      </c>
+      <c r="BT19" t="n">
+        <v>11786</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>425</v>
+        <v>554</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -3810,10 +4779,61 @@
       <c r="BC20" t="n">
         <v>4597</v>
       </c>
+      <c r="BD20" t="n">
+        <v>4622</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4622</v>
+      </c>
+      <c r="BF20" t="n">
+        <v>4655</v>
+      </c>
+      <c r="BG20" t="n">
+        <v>4760</v>
+      </c>
+      <c r="BH20" t="n">
+        <v>4760</v>
+      </c>
+      <c r="BI20" t="n">
+        <v>4760</v>
+      </c>
+      <c r="BJ20" t="n">
+        <v>4760</v>
+      </c>
+      <c r="BK20" t="n">
+        <v>4760</v>
+      </c>
+      <c r="BL20" t="n">
+        <v>4830</v>
+      </c>
+      <c r="BM20" t="n">
+        <v>4830</v>
+      </c>
+      <c r="BN20" t="n">
+        <v>4830</v>
+      </c>
+      <c r="BO20" t="n">
+        <v>4830</v>
+      </c>
+      <c r="BP20" t="n">
+        <v>4857</v>
+      </c>
+      <c r="BQ20" t="n">
+        <v>4924</v>
+      </c>
+      <c r="BR20" t="n">
+        <v>5055</v>
+      </c>
+      <c r="BS20" t="n">
+        <v>5186</v>
+      </c>
+      <c r="BT20" t="n">
+        <v>5186</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>459</v>
+        <v>595</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -3979,10 +4999,61 @@
       <c r="BC21" t="n">
         <v>2395</v>
       </c>
+      <c r="BD21" t="n">
+        <v>2398</v>
+      </c>
+      <c r="BE21" t="n">
+        <v>2428</v>
+      </c>
+      <c r="BF21" t="n">
+        <v>2428</v>
+      </c>
+      <c r="BG21" t="n">
+        <v>2455</v>
+      </c>
+      <c r="BH21" t="n">
+        <v>2489</v>
+      </c>
+      <c r="BI21" t="n">
+        <v>2560</v>
+      </c>
+      <c r="BJ21" t="n">
+        <v>2591</v>
+      </c>
+      <c r="BK21" t="n">
+        <v>2637</v>
+      </c>
+      <c r="BL21" t="n">
+        <v>2687</v>
+      </c>
+      <c r="BM21" t="n">
+        <v>2715</v>
+      </c>
+      <c r="BN21" t="n">
+        <v>2737</v>
+      </c>
+      <c r="BO21" t="n">
+        <v>2769</v>
+      </c>
+      <c r="BP21" t="n">
+        <v>2780</v>
+      </c>
+      <c r="BQ21" t="n">
+        <v>2805</v>
+      </c>
+      <c r="BR21" t="n">
+        <v>2851</v>
+      </c>
+      <c r="BS21" t="n">
+        <v>2918</v>
+      </c>
+      <c r="BT21" t="n">
+        <v>2924</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>525</v>
+        <v>683</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -4148,10 +5219,61 @@
       <c r="BC22" t="n">
         <v>11743</v>
       </c>
+      <c r="BD22" t="n">
+        <v>11980</v>
+      </c>
+      <c r="BE22" t="n">
+        <v>12237</v>
+      </c>
+      <c r="BF22" t="n">
+        <v>12450</v>
+      </c>
+      <c r="BG22" t="n">
+        <v>12618</v>
+      </c>
+      <c r="BH22" t="n">
+        <v>12819</v>
+      </c>
+      <c r="BI22" t="n">
+        <v>12991</v>
+      </c>
+      <c r="BJ22" t="n">
+        <v>13190</v>
+      </c>
+      <c r="BK22" t="n">
+        <v>13475</v>
+      </c>
+      <c r="BL22" t="n">
+        <v>13695</v>
+      </c>
+      <c r="BM22" t="n">
+        <v>13963</v>
+      </c>
+      <c r="BN22" t="n">
+        <v>14210</v>
+      </c>
+      <c r="BO22" t="n">
+        <v>14410</v>
+      </c>
+      <c r="BP22" t="n">
+        <v>14565</v>
+      </c>
+      <c r="BQ22" t="n">
+        <v>14792</v>
+      </c>
+      <c r="BR22" t="n">
+        <v>15110</v>
+      </c>
+      <c r="BS22" t="n">
+        <v>15263</v>
+      </c>
+      <c r="BT22" t="n">
+        <v>15532</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>545</v>
+        <v>712</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -4317,10 +5439,61 @@
       <c r="BC23" t="n">
         <v>1516</v>
       </c>
+      <c r="BD23" t="n">
+        <v>1526</v>
+      </c>
+      <c r="BE23" t="n">
+        <v>1571</v>
+      </c>
+      <c r="BF23" t="n">
+        <v>1584</v>
+      </c>
+      <c r="BG23" t="n">
+        <v>1602</v>
+      </c>
+      <c r="BH23" t="n">
+        <v>1632</v>
+      </c>
+      <c r="BI23" t="n">
+        <v>1636</v>
+      </c>
+      <c r="BJ23" t="n">
+        <v>1640</v>
+      </c>
+      <c r="BK23" t="n">
+        <v>1670</v>
+      </c>
+      <c r="BL23" t="n">
+        <v>1670</v>
+      </c>
+      <c r="BM23" t="n">
+        <v>1670</v>
+      </c>
+      <c r="BN23" t="n">
+        <v>1672</v>
+      </c>
+      <c r="BO23" t="n">
+        <v>1672</v>
+      </c>
+      <c r="BP23" t="n">
+        <v>1680</v>
+      </c>
+      <c r="BQ23" t="n">
+        <v>1695</v>
+      </c>
+      <c r="BR23" t="n">
+        <v>1697</v>
+      </c>
+      <c r="BS23" t="n">
+        <v>1720</v>
+      </c>
+      <c r="BT23" t="n">
+        <v>1858</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>578</v>
+        <v>757</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -4486,10 +5659,61 @@
       <c r="BC24" t="n">
         <v>222</v>
       </c>
+      <c r="BD24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BE24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BF24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BG24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BH24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BI24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BJ24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BK24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BL24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BM24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BN24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BO24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BP24" t="n">
+        <v>223</v>
+      </c>
+      <c r="BQ24" t="n">
+        <v>229</v>
+      </c>
+      <c r="BR24" t="n">
+        <v>250</v>
+      </c>
+      <c r="BS24" t="n">
+        <v>250</v>
+      </c>
+      <c r="BT24" t="n">
+        <v>250</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>597</v>
+        <v>784</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -4655,10 +5879,61 @@
       <c r="BC25" t="n">
         <v>9116</v>
       </c>
+      <c r="BD25" t="n">
+        <v>9237</v>
+      </c>
+      <c r="BE25" t="n">
+        <v>9306</v>
+      </c>
+      <c r="BF25" t="n">
+        <v>9474</v>
+      </c>
+      <c r="BG25" t="n">
+        <v>9495</v>
+      </c>
+      <c r="BH25" t="n">
+        <v>9668</v>
+      </c>
+      <c r="BI25" t="n">
+        <v>9772</v>
+      </c>
+      <c r="BJ25" t="n">
+        <v>9970</v>
+      </c>
+      <c r="BK25" t="n">
+        <v>10265</v>
+      </c>
+      <c r="BL25" t="n">
+        <v>10382</v>
+      </c>
+      <c r="BM25" t="n">
+        <v>10422</v>
+      </c>
+      <c r="BN25" t="n">
+        <v>10451</v>
+      </c>
+      <c r="BO25" t="n">
+        <v>10471</v>
+      </c>
+      <c r="BP25" t="n">
+        <v>10516</v>
+      </c>
+      <c r="BQ25" t="n">
+        <v>10707</v>
+      </c>
+      <c r="BR25" t="n">
+        <v>10804</v>
+      </c>
+      <c r="BS25" t="n">
+        <v>11161</v>
+      </c>
+      <c r="BT25" t="n">
+        <v>11287</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>681</v>
+        <v>892</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -4824,10 +6099,61 @@
       <c r="BC26" t="n">
         <v>23360</v>
       </c>
+      <c r="BD26" t="n">
+        <v>23742</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>24012</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>24426</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>24902</v>
+      </c>
+      <c r="BH26" t="n">
+        <v>25214</v>
+      </c>
+      <c r="BI26" t="n">
+        <v>25958</v>
+      </c>
+      <c r="BJ26" t="n">
+        <v>26246</v>
+      </c>
+      <c r="BK26" t="n">
+        <v>26823</v>
+      </c>
+      <c r="BL26" t="n">
+        <v>26966</v>
+      </c>
+      <c r="BM26" t="n">
+        <v>27336</v>
+      </c>
+      <c r="BN26" t="n">
+        <v>28055</v>
+      </c>
+      <c r="BO26" t="n">
+        <v>28513</v>
+      </c>
+      <c r="BP26" t="n">
+        <v>28851</v>
+      </c>
+      <c r="BQ26" t="n">
+        <v>29218</v>
+      </c>
+      <c r="BR26" t="n">
+        <v>30081</v>
+      </c>
+      <c r="BS26" t="n">
+        <v>30517</v>
+      </c>
+      <c r="BT26" t="n">
+        <v>30921</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>682</v>
+        <v>895</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -4993,10 +6319,61 @@
       <c r="BC27" t="n">
         <v>755</v>
       </c>
+      <c r="BD27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BH27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BI27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BJ27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BK27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BL27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BM27" t="n">
+        <v>755</v>
+      </c>
+      <c r="BN27" t="n">
+        <v>758</v>
+      </c>
+      <c r="BO27" t="n">
+        <v>758</v>
+      </c>
+      <c r="BP27" t="n">
+        <v>758</v>
+      </c>
+      <c r="BQ27" t="n">
+        <v>758</v>
+      </c>
+      <c r="BR27" t="n">
+        <v>758</v>
+      </c>
+      <c r="BS27" t="n">
+        <v>759</v>
+      </c>
+      <c r="BT27" t="n">
+        <v>759</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>695</v>
+        <v>922</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -5162,1873 +6539,2485 @@
       <c r="BC28" t="n">
         <v>7951</v>
       </c>
+      <c r="BD28" t="n">
+        <v>8124</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>8346</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>8527</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>8766</v>
+      </c>
+      <c r="BH28" t="n">
+        <v>9025</v>
+      </c>
+      <c r="BI28" t="n">
+        <v>9269</v>
+      </c>
+      <c r="BJ28" t="n">
+        <v>9462</v>
+      </c>
+      <c r="BK28" t="n">
+        <v>9841</v>
+      </c>
+      <c r="BL28" t="n">
+        <v>10049</v>
+      </c>
+      <c r="BM28" t="n">
+        <v>10379</v>
+      </c>
+      <c r="BN28" t="n">
+        <v>10912</v>
+      </c>
+      <c r="BO28" t="n">
+        <v>11216</v>
+      </c>
+      <c r="BP28" t="n">
+        <v>11501</v>
+      </c>
+      <c r="BQ28" t="n">
+        <v>11857</v>
+      </c>
+      <c r="BR28" t="n">
+        <v>12355</v>
+      </c>
+      <c r="BS28" t="n">
+        <v>12677</v>
+      </c>
+      <c r="BT28" t="n">
+        <v>12950</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>794</v>
+        <v>990</v>
       </c>
       <c r="B29" t="inlineStr">
+        <is>
+          <t>hellrazor_0</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>7</v>
+      </c>
+      <c r="D29" t="n">
+        <v>74</v>
+      </c>
+      <c r="E29" t="n">
+        <v>122</v>
+      </c>
+      <c r="F29" t="n">
+        <v>158</v>
+      </c>
+      <c r="G29" t="n">
+        <v>227</v>
+      </c>
+      <c r="H29" t="n">
+        <v>255</v>
+      </c>
+      <c r="I29" t="n">
+        <v>310</v>
+      </c>
+      <c r="J29" t="n">
+        <v>383</v>
+      </c>
+      <c r="K29" t="n">
+        <v>448</v>
+      </c>
+      <c r="L29" t="n">
+        <v>499</v>
+      </c>
+      <c r="M29" t="n">
+        <v>554</v>
+      </c>
+      <c r="N29" t="n">
+        <v>609</v>
+      </c>
+      <c r="O29" t="n">
+        <v>716</v>
+      </c>
+      <c r="P29" t="n">
+        <v>831</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>861</v>
+      </c>
+      <c r="R29" t="n">
+        <v>891</v>
+      </c>
+      <c r="S29" t="n">
+        <v>968</v>
+      </c>
+      <c r="T29" t="n">
+        <v>979</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1039</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1073</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1146</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1226</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1256</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1416</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1440</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1517</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1734</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1770</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1829</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1872</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>2153</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2196</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>2223</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>2428</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>2529</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>2615</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>2842</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>2842</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>2859</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>2957</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>3069</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>3117</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>3132</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>3212</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>3239</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>3269</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>3305</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>3314</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>3488</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>3539</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>3650</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>3766</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>3779</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>3887</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>3986</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>4092</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>4191</v>
+      </c>
+      <c r="BH29" t="n">
+        <v>4278</v>
+      </c>
+      <c r="BI29" t="n">
+        <v>4345</v>
+      </c>
+      <c r="BJ29" t="n">
+        <v>4391</v>
+      </c>
+      <c r="BK29" t="n">
+        <v>4536</v>
+      </c>
+      <c r="BL29" t="n">
+        <v>4659</v>
+      </c>
+      <c r="BM29" t="n">
+        <v>4692</v>
+      </c>
+      <c r="BN29" t="n">
+        <v>4859</v>
+      </c>
+      <c r="BO29" t="n">
+        <v>4965</v>
+      </c>
+      <c r="BP29" t="n">
+        <v>5019</v>
+      </c>
+      <c r="BQ29" t="n">
+        <v>5168</v>
+      </c>
+      <c r="BR29" t="n">
+        <v>5369</v>
+      </c>
+      <c r="BS29" t="n">
+        <v>5402</v>
+      </c>
+      <c r="BT29" t="n">
+        <v>5546</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>1046</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>itsTyloh</t>
         </is>
       </c>
-      <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="n">
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
         <v>112</v>
       </c>
-      <c r="E29" t="n">
+      <c r="E30" t="n">
         <v>119</v>
       </c>
-      <c r="F29" t="n">
+      <c r="F30" t="n">
         <v>140</v>
       </c>
-      <c r="G29" t="n">
+      <c r="G30" t="n">
         <v>162</v>
       </c>
-      <c r="H29" t="n">
+      <c r="H30" t="n">
         <v>162</v>
       </c>
-      <c r="I29" t="n">
+      <c r="I30" t="n">
         <v>192</v>
       </c>
-      <c r="J29" t="n">
+      <c r="J30" t="n">
         <v>227</v>
       </c>
-      <c r="K29" t="n">
+      <c r="K30" t="n">
         <v>227</v>
       </c>
-      <c r="L29" t="n">
+      <c r="L30" t="n">
         <v>227</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M30" t="n">
         <v>227</v>
       </c>
-      <c r="N29" t="n">
+      <c r="N30" t="n">
         <v>227</v>
       </c>
-      <c r="O29" t="n">
+      <c r="O30" t="n">
         <v>227</v>
       </c>
-      <c r="P29" t="n">
+      <c r="P30" t="n">
         <v>276</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="Q30" t="n">
         <v>299</v>
       </c>
-      <c r="R29" t="n">
+      <c r="R30" t="n">
         <v>309</v>
       </c>
-      <c r="S29" t="n">
+      <c r="S30" t="n">
         <v>383</v>
       </c>
-      <c r="T29" t="n">
+      <c r="T30" t="n">
         <v>383</v>
       </c>
-      <c r="U29" t="n">
+      <c r="U30" t="n">
         <v>389</v>
       </c>
-      <c r="V29" t="n">
+      <c r="V30" t="n">
         <v>403</v>
       </c>
-      <c r="W29" t="n">
+      <c r="W30" t="n">
         <v>414</v>
       </c>
-      <c r="X29" t="n">
+      <c r="X30" t="n">
         <v>418</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="Y30" t="n">
         <v>418</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="Z30" t="n">
         <v>436</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AA30" t="n">
         <v>442</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AB30" t="n">
         <v>442</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AC30" t="n">
         <v>442</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AD30" t="n">
         <v>442</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AE30" t="n">
         <v>442</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AF30" t="n">
         <v>442</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AG30" t="n">
         <v>442</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AH30" t="n">
         <v>442</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AI30" t="n">
         <v>442</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AJ30" t="n">
         <v>442</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AK30" t="n">
         <v>442</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AL30" t="n">
         <v>442</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AM30" t="n">
         <v>442</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AN30" t="n">
         <v>442</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AO30" t="n">
         <v>442</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AP30" t="n">
         <v>442</v>
       </c>
-      <c r="AQ29" t="n">
+      <c r="AQ30" t="n">
         <v>442</v>
       </c>
-      <c r="AR29" t="n">
+      <c r="AR30" t="n">
         <v>442</v>
       </c>
-      <c r="AS29" t="n">
+      <c r="AS30" t="n">
         <v>442</v>
       </c>
-      <c r="AT29" t="n">
+      <c r="AT30" t="n">
         <v>442</v>
       </c>
-      <c r="AU29" t="n">
+      <c r="AU30" t="n">
         <v>442</v>
       </c>
-      <c r="AV29" t="n">
+      <c r="AV30" t="n">
         <v>442</v>
       </c>
-      <c r="AW29" t="n">
+      <c r="AW30" t="n">
         <v>442</v>
       </c>
-      <c r="AX29" t="n">
+      <c r="AX30" t="n">
         <v>442</v>
       </c>
-      <c r="AY29" t="n">
+      <c r="AY30" t="n">
         <v>448</v>
       </c>
-      <c r="AZ29" t="n">
+      <c r="AZ30" t="n">
         <v>450</v>
       </c>
-      <c r="BA29" t="n">
+      <c r="BA30" t="n">
         <v>450</v>
       </c>
-      <c r="BB29" t="n">
+      <c r="BB30" t="n">
         <v>450</v>
       </c>
-      <c r="BC29" t="n">
+      <c r="BC30" t="n">
         <v>450</v>
       </c>
+      <c r="BD30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BH30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BI30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BJ30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BK30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BL30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BM30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BN30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BO30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BP30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BQ30" t="n">
+        <v>450</v>
+      </c>
+      <c r="BR30" t="n">
+        <v>453</v>
+      </c>
+      <c r="BS30" t="n">
+        <v>453</v>
+      </c>
+      <c r="BT30" t="n">
+        <v>453</v>
+      </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>893</v>
-      </c>
-      <c r="B30" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>1169</v>
+      </c>
+      <c r="B31" t="inlineStr">
         <is>
           <t>lajoss__</t>
         </is>
       </c>
-      <c r="C30" t="n">
+      <c r="C31" t="n">
         <v>193</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D31" t="n">
         <v>353</v>
       </c>
-      <c r="E30" t="n">
+      <c r="E31" t="n">
         <v>353</v>
       </c>
-      <c r="F30" t="n">
+      <c r="F31" t="n">
         <v>1023</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G31" t="n">
         <v>1409</v>
       </c>
-      <c r="H30" t="n">
+      <c r="H31" t="n">
         <v>1746</v>
       </c>
-      <c r="I30" t="n">
+      <c r="I31" t="n">
         <v>2464</v>
       </c>
-      <c r="J30" t="n">
+      <c r="J31" t="n">
         <v>2955</v>
       </c>
-      <c r="K30" t="n">
+      <c r="K31" t="n">
         <v>3273</v>
       </c>
-      <c r="L30" t="n">
+      <c r="L31" t="n">
         <v>3648</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M31" t="n">
         <v>4187</v>
       </c>
-      <c r="N30" t="n">
+      <c r="N31" t="n">
         <v>4748</v>
       </c>
-      <c r="O30" t="n">
+      <c r="O31" t="n">
         <v>5217</v>
       </c>
-      <c r="P30" t="n">
+      <c r="P31" t="n">
         <v>5217</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="Q31" t="n">
         <v>5670</v>
       </c>
-      <c r="R30" t="n">
+      <c r="R31" t="n">
         <v>6154</v>
       </c>
-      <c r="S30" t="n">
+      <c r="S31" t="n">
         <v>6644</v>
       </c>
-      <c r="T30" t="n">
+      <c r="T31" t="n">
         <v>6645</v>
       </c>
-      <c r="U30" t="n">
+      <c r="U31" t="n">
         <v>6906</v>
       </c>
-      <c r="V30" t="n">
+      <c r="V31" t="n">
         <v>6984</v>
       </c>
-      <c r="W30" t="n">
+      <c r="W31" t="n">
         <v>7178</v>
       </c>
-      <c r="X30" t="n">
+      <c r="X31" t="n">
         <v>7667</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="Y31" t="n">
         <v>8038</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="Z31" t="n">
         <v>8099</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AA31" t="n">
         <v>8315</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AB31" t="n">
         <v>8669</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AC31" t="n">
         <v>9321</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AD31" t="n">
         <v>9468</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AE31" t="n">
         <v>9675</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AF31" t="n">
         <v>9855</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AG31" t="n">
         <v>9972</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AH31" t="n">
         <v>10158</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AI31" t="n">
         <v>10486</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AJ31" t="n">
         <v>10788</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AK31" t="n">
         <v>11022</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AL31" t="n">
         <v>11107</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AM31" t="n">
         <v>11123</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AN31" t="n">
         <v>11123</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AO31" t="n">
         <v>11157</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AP31" t="n">
         <v>11157</v>
       </c>
-      <c r="AQ30" t="n">
+      <c r="AQ31" t="n">
         <v>11323</v>
       </c>
-      <c r="AR30" t="n">
+      <c r="AR31" t="n">
         <v>11369</v>
       </c>
-      <c r="AS30" t="n">
+      <c r="AS31" t="n">
         <v>11466</v>
       </c>
-      <c r="AT30" t="n">
+      <c r="AT31" t="n">
         <v>11699</v>
       </c>
-      <c r="AU30" t="n">
+      <c r="AU31" t="n">
         <v>11706</v>
       </c>
-      <c r="AV30" t="n">
+      <c r="AV31" t="n">
         <v>11706</v>
       </c>
-      <c r="AW30" t="n">
+      <c r="AW31" t="n">
         <v>11706</v>
       </c>
-      <c r="AX30" t="n">
+      <c r="AX31" t="n">
         <v>11950</v>
       </c>
-      <c r="AY30" t="n">
+      <c r="AY31" t="n">
         <v>11950</v>
       </c>
-      <c r="AZ30" t="n">
+      <c r="AZ31" t="n">
         <v>11959</v>
       </c>
-      <c r="BA30" t="n">
+      <c r="BA31" t="n">
         <v>12171</v>
       </c>
-      <c r="BB30" t="n">
+      <c r="BB31" t="n">
         <v>12306</v>
       </c>
-      <c r="BC30" t="n">
+      <c r="BC31" t="n">
         <v>12306</v>
       </c>
+      <c r="BD31" t="n">
+        <v>12310</v>
+      </c>
+      <c r="BE31" t="n">
+        <v>12628</v>
+      </c>
+      <c r="BF31" t="n">
+        <v>13064</v>
+      </c>
+      <c r="BG31" t="n">
+        <v>13064</v>
+      </c>
+      <c r="BH31" t="n">
+        <v>13229</v>
+      </c>
+      <c r="BI31" t="n">
+        <v>13475</v>
+      </c>
+      <c r="BJ31" t="n">
+        <v>13477</v>
+      </c>
+      <c r="BK31" t="n">
+        <v>13899</v>
+      </c>
+      <c r="BL31" t="n">
+        <v>14042</v>
+      </c>
+      <c r="BM31" t="n">
+        <v>14042</v>
+      </c>
+      <c r="BN31" t="n">
+        <v>14191</v>
+      </c>
+      <c r="BO31" t="n">
+        <v>14394</v>
+      </c>
+      <c r="BP31" t="n">
+        <v>14394</v>
+      </c>
+      <c r="BQ31" t="n">
+        <v>14426</v>
+      </c>
+      <c r="BR31" t="n">
+        <v>14626</v>
+      </c>
+      <c r="BS31" t="n">
+        <v>14626</v>
+      </c>
+      <c r="BT31" t="n">
+        <v>14682</v>
+      </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>994</v>
-      </c>
-      <c r="B31" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>1303</v>
+      </c>
+      <c r="B32" t="inlineStr">
         <is>
           <t>nishad13</t>
         </is>
       </c>
-      <c r="C31" t="n">
+      <c r="C32" t="n">
         <v>196</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D32" t="n">
         <v>772</v>
       </c>
-      <c r="E31" t="n">
+      <c r="E32" t="n">
         <v>1205</v>
       </c>
-      <c r="F31" t="n">
+      <c r="F32" t="n">
         <v>2134</v>
       </c>
-      <c r="G31" t="n">
+      <c r="G32" t="n">
         <v>2904</v>
       </c>
-      <c r="H31" t="n">
+      <c r="H32" t="n">
         <v>3452</v>
       </c>
-      <c r="I31" t="n">
+      <c r="I32" t="n">
         <v>4301</v>
       </c>
-      <c r="J31" t="n">
+      <c r="J32" t="n">
         <v>5130</v>
       </c>
-      <c r="K31" t="n">
+      <c r="K32" t="n">
         <v>5690</v>
       </c>
-      <c r="L31" t="n">
+      <c r="L32" t="n">
         <v>6424</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M32" t="n">
         <v>6929</v>
       </c>
-      <c r="N31" t="n">
+      <c r="N32" t="n">
         <v>7223</v>
       </c>
-      <c r="O31" t="n">
+      <c r="O32" t="n">
         <v>7557</v>
       </c>
-      <c r="P31" t="n">
+      <c r="P32" t="n">
         <v>7578</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="Q32" t="n">
         <v>7638</v>
       </c>
-      <c r="R31" t="n">
+      <c r="R32" t="n">
         <v>7674</v>
       </c>
-      <c r="S31" t="n">
+      <c r="S32" t="n">
         <v>7719</v>
       </c>
-      <c r="T31" t="n">
+      <c r="T32" t="n">
         <v>7735</v>
       </c>
-      <c r="U31" t="n">
+      <c r="U32" t="n">
         <v>7736</v>
       </c>
-      <c r="V31" t="n">
+      <c r="V32" t="n">
         <v>7753</v>
       </c>
-      <c r="W31" t="n">
+      <c r="W32" t="n">
         <v>7777</v>
       </c>
-      <c r="X31" t="n">
+      <c r="X32" t="n">
         <v>7839</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="Y32" t="n">
         <v>8113</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="Z32" t="n">
         <v>8168</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AA32" t="n">
         <v>8168</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AB32" t="n">
         <v>8463</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AC32" t="n">
         <v>8777</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AD32" t="n">
         <v>9057</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AE32" t="n">
         <v>9373</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AF32" t="n">
         <v>9373</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AG32" t="n">
         <v>9513</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AH32" t="n">
         <v>10195</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AI32" t="n">
         <v>10334</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AJ32" t="n">
         <v>10468</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AK32" t="n">
         <v>10538</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AL32" t="n">
         <v>10538</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AM32" t="n">
         <v>10955</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AN32" t="n">
         <v>10990</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AO32" t="n">
         <v>11665</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AP32" t="n">
         <v>12088</v>
       </c>
-      <c r="AQ31" t="n">
+      <c r="AQ32" t="n">
         <v>12966</v>
       </c>
-      <c r="AR31" t="n">
+      <c r="AR32" t="n">
         <v>13307</v>
       </c>
-      <c r="AS31" t="n">
+      <c r="AS32" t="n">
         <v>13994</v>
       </c>
-      <c r="AT31" t="n">
+      <c r="AT32" t="n">
         <v>14858</v>
       </c>
-      <c r="AU31" t="n">
+      <c r="AU32" t="n">
         <v>15795</v>
       </c>
-      <c r="AV31" t="n">
+      <c r="AV32" t="n">
         <v>16900</v>
       </c>
-      <c r="AW31" t="n">
+      <c r="AW32" t="n">
         <v>17213</v>
       </c>
-      <c r="AX31" t="n">
+      <c r="AX32" t="n">
         <v>18196</v>
       </c>
-      <c r="AY31" t="n">
+      <c r="AY32" t="n">
         <v>18497</v>
       </c>
-      <c r="AZ31" t="n">
+      <c r="AZ32" t="n">
         <v>18920</v>
       </c>
-      <c r="BA31" t="n">
+      <c r="BA32" t="n">
         <v>19321</v>
       </c>
-      <c r="BB31" t="n">
+      <c r="BB32" t="n">
         <v>19362</v>
       </c>
-      <c r="BC31" t="n">
+      <c r="BC32" t="n">
         <v>19856</v>
       </c>
+      <c r="BD32" t="n">
+        <v>19951</v>
+      </c>
+      <c r="BE32" t="n">
+        <v>20117</v>
+      </c>
+      <c r="BF32" t="n">
+        <v>20863</v>
+      </c>
+      <c r="BG32" t="n">
+        <v>21558</v>
+      </c>
+      <c r="BH32" t="n">
+        <v>21981</v>
+      </c>
+      <c r="BI32" t="n">
+        <v>22664</v>
+      </c>
+      <c r="BJ32" t="n">
+        <v>23460</v>
+      </c>
+      <c r="BK32" t="n">
+        <v>24244</v>
+      </c>
+      <c r="BL32" t="n">
+        <v>24588</v>
+      </c>
+      <c r="BM32" t="n">
+        <v>25078</v>
+      </c>
+      <c r="BN32" t="n">
+        <v>25481</v>
+      </c>
+      <c r="BO32" t="n">
+        <v>25990</v>
+      </c>
+      <c r="BP32" t="n">
+        <v>26637</v>
+      </c>
+      <c r="BQ32" t="n">
+        <v>27746</v>
+      </c>
+      <c r="BR32" t="n">
+        <v>28710</v>
+      </c>
+      <c r="BS32" t="n">
+        <v>29222</v>
+      </c>
+      <c r="BT32" t="n">
+        <v>30026</v>
+      </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>1050</v>
-      </c>
-      <c r="B32" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>1377</v>
+      </c>
+      <c r="B33" t="inlineStr">
         <is>
           <t>polimpompis</t>
         </is>
       </c>
-      <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" t="n">
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
         <v>55</v>
       </c>
-      <c r="F32" t="n">
+      <c r="F33" t="n">
         <v>151</v>
       </c>
-      <c r="G32" t="n">
+      <c r="G33" t="n">
         <v>447</v>
       </c>
-      <c r="H32" t="n">
+      <c r="H33" t="n">
         <v>694</v>
       </c>
-      <c r="I32" t="n">
+      <c r="I33" t="n">
         <v>1164</v>
       </c>
-      <c r="J32" t="n">
+      <c r="J33" t="n">
         <v>1656</v>
       </c>
-      <c r="K32" t="n">
+      <c r="K33" t="n">
         <v>1740</v>
       </c>
-      <c r="L32" t="n">
+      <c r="L33" t="n">
         <v>2395</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M33" t="n">
         <v>2582</v>
       </c>
-      <c r="N32" t="n">
+      <c r="N33" t="n">
         <v>2879</v>
       </c>
-      <c r="O32" t="n">
+      <c r="O33" t="n">
         <v>3301</v>
       </c>
-      <c r="P32" t="n">
+      <c r="P33" t="n">
         <v>3999</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="Q33" t="n">
         <v>4832</v>
       </c>
-      <c r="R32" t="n">
+      <c r="R33" t="n">
         <v>5053</v>
       </c>
-      <c r="S32" t="n">
+      <c r="S33" t="n">
         <v>5902</v>
       </c>
-      <c r="T32" t="n">
+      <c r="T33" t="n">
         <v>6332</v>
       </c>
-      <c r="U32" t="n">
+      <c r="U33" t="n">
         <v>6971</v>
       </c>
-      <c r="V32" t="n">
+      <c r="V33" t="n">
         <v>7733</v>
       </c>
-      <c r="W32" t="n">
+      <c r="W33" t="n">
         <v>8534</v>
       </c>
-      <c r="X32" t="n">
+      <c r="X33" t="n">
         <v>9445</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="Y33" t="n">
         <v>10113</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="Z33" t="n">
         <v>10468</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AA33" t="n">
         <v>10773</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AB33" t="n">
         <v>11323</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AC33" t="n">
         <v>12395</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AD33" t="n">
         <v>12435</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AE33" t="n">
         <v>12804</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AF33" t="n">
         <v>12962</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AG33" t="n">
         <v>13457</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AH33" t="n">
         <v>13471</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AI33" t="n">
         <v>13755</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AJ33" t="n">
         <v>14446</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AK33" t="n">
         <v>14706</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AL33" t="n">
         <v>14887</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AM33" t="n">
         <v>15281</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AN33" t="n">
         <v>15324</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AO33" t="n">
         <v>15378</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AP33" t="n">
         <v>15662</v>
       </c>
-      <c r="AQ32" t="n">
+      <c r="AQ33" t="n">
         <v>15662</v>
       </c>
-      <c r="AR32" t="n">
+      <c r="AR33" t="n">
         <v>15663</v>
       </c>
-      <c r="AS32" t="n">
+      <c r="AS33" t="n">
         <v>16290</v>
       </c>
-      <c r="AT32" t="n">
+      <c r="AT33" t="n">
         <v>16763</v>
       </c>
-      <c r="AU32" t="n">
+      <c r="AU33" t="n">
         <v>17404</v>
       </c>
-      <c r="AV32" t="n">
+      <c r="AV33" t="n">
         <v>17972</v>
       </c>
-      <c r="AW32" t="n">
+      <c r="AW33" t="n">
         <v>18388</v>
       </c>
-      <c r="AX32" t="n">
+      <c r="AX33" t="n">
         <v>19394</v>
       </c>
-      <c r="AY32" t="n">
+      <c r="AY33" t="n">
         <v>19914</v>
       </c>
-      <c r="AZ32" t="n">
+      <c r="AZ33" t="n">
         <v>20780</v>
       </c>
-      <c r="BA32" t="n">
+      <c r="BA33" t="n">
         <v>21308</v>
       </c>
-      <c r="BB32" t="n">
+      <c r="BB33" t="n">
         <v>21519</v>
       </c>
-      <c r="BC32" t="n">
+      <c r="BC33" t="n">
         <v>21871</v>
       </c>
+      <c r="BD33" t="n">
+        <v>22542</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>22545</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>23002</v>
+      </c>
+      <c r="BG33" t="n">
+        <v>23381</v>
+      </c>
+      <c r="BH33" t="n">
+        <v>23446</v>
+      </c>
+      <c r="BI33" t="n">
+        <v>24294</v>
+      </c>
+      <c r="BJ33" t="n">
+        <v>25073</v>
+      </c>
+      <c r="BK33" t="n">
+        <v>25547</v>
+      </c>
+      <c r="BL33" t="n">
+        <v>25630</v>
+      </c>
+      <c r="BM33" t="n">
+        <v>25783</v>
+      </c>
+      <c r="BN33" t="n">
+        <v>26318</v>
+      </c>
+      <c r="BO33" t="n">
+        <v>26441</v>
+      </c>
+      <c r="BP33" t="n">
+        <v>26775</v>
+      </c>
+      <c r="BQ33" t="n">
+        <v>27140</v>
+      </c>
+      <c r="BR33" t="n">
+        <v>27867</v>
+      </c>
+      <c r="BS33" t="n">
+        <v>28471</v>
+      </c>
+      <c r="BT33" t="n">
+        <v>29200</v>
+      </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>1062</v>
-      </c>
-      <c r="B33" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>1394</v>
+      </c>
+      <c r="B34" t="inlineStr">
         <is>
           <t>rafa30___</t>
         </is>
       </c>
-      <c r="C33" t="n">
+      <c r="C34" t="n">
         <v>233</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D34" t="n">
         <v>719</v>
       </c>
-      <c r="E33" t="n">
+      <c r="E34" t="n">
         <v>1013</v>
       </c>
-      <c r="F33" t="n">
+      <c r="F34" t="n">
         <v>1932</v>
       </c>
-      <c r="G33" t="n">
+      <c r="G34" t="n">
         <v>2426</v>
       </c>
-      <c r="H33" t="n">
+      <c r="H34" t="n">
         <v>2599</v>
       </c>
-      <c r="I33" t="n">
+      <c r="I34" t="n">
         <v>3251</v>
       </c>
-      <c r="J33" t="n">
+      <c r="J34" t="n">
         <v>3746</v>
       </c>
-      <c r="K33" t="n">
+      <c r="K34" t="n">
         <v>4185</v>
       </c>
-      <c r="L33" t="n">
+      <c r="L34" t="n">
         <v>4553</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M34" t="n">
         <v>4965</v>
       </c>
-      <c r="N33" t="n">
+      <c r="N34" t="n">
         <v>5326</v>
       </c>
-      <c r="O33" t="n">
+      <c r="O34" t="n">
         <v>5830</v>
       </c>
-      <c r="P33" t="n">
+      <c r="P34" t="n">
         <v>6397</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="Q34" t="n">
         <v>6867</v>
       </c>
-      <c r="R33" t="n">
+      <c r="R34" t="n">
         <v>7164</v>
       </c>
-      <c r="S33" t="n">
+      <c r="S34" t="n">
         <v>7537</v>
       </c>
-      <c r="T33" t="n">
+      <c r="T34" t="n">
         <v>7852</v>
       </c>
-      <c r="U33" t="n">
+      <c r="U34" t="n">
         <v>8164</v>
       </c>
-      <c r="V33" t="n">
+      <c r="V34" t="n">
         <v>8654</v>
       </c>
-      <c r="W33" t="n">
+      <c r="W34" t="n">
         <v>9133</v>
       </c>
-      <c r="X33" t="n">
+      <c r="X34" t="n">
         <v>9731</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="Y34" t="n">
         <v>10162</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="Z34" t="n">
         <v>10635</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AA34" t="n">
         <v>11057</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AB34" t="n">
         <v>11563</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AC34" t="n">
         <v>12309</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AD34" t="n">
         <v>12428</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AE34" t="n">
         <v>12537</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AF34" t="n">
         <v>12698</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AG34" t="n">
         <v>13145</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AH34" t="n">
         <v>13443</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AI34" t="n">
         <v>13643</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AJ34" t="n">
         <v>14273</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AK34" t="n">
         <v>14610</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AL34" t="n">
         <v>14800</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AM34" t="n">
         <v>15228</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AN34" t="n">
         <v>15305</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AO34" t="n">
         <v>15620</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AP34" t="n">
         <v>16105</v>
       </c>
-      <c r="AQ33" t="n">
+      <c r="AQ34" t="n">
         <v>16421</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AR34" t="n">
         <v>16571</v>
       </c>
-      <c r="AS33" t="n">
+      <c r="AS34" t="n">
         <v>17109</v>
       </c>
-      <c r="AT33" t="n">
+      <c r="AT34" t="n">
         <v>18132</v>
       </c>
-      <c r="AU33" t="n">
+      <c r="AU34" t="n">
         <v>18762</v>
       </c>
-      <c r="AV33" t="n">
+      <c r="AV34" t="n">
         <v>19424</v>
       </c>
-      <c r="AW33" t="n">
+      <c r="AW34" t="n">
         <v>19800</v>
       </c>
-      <c r="AX33" t="n">
+      <c r="AX34" t="n">
         <v>20421</v>
       </c>
-      <c r="AY33" t="n">
+      <c r="AY34" t="n">
         <v>20690</v>
       </c>
-      <c r="AZ33" t="n">
+      <c r="AZ34" t="n">
         <v>21368</v>
       </c>
-      <c r="BA33" t="n">
+      <c r="BA34" t="n">
         <v>21810</v>
       </c>
-      <c r="BB33" t="n">
+      <c r="BB34" t="n">
         <v>22379</v>
       </c>
-      <c r="BC33" t="n">
+      <c r="BC34" t="n">
         <v>22895</v>
       </c>
+      <c r="BD34" t="n">
+        <v>23226</v>
+      </c>
+      <c r="BE34" t="n">
+        <v>23501</v>
+      </c>
+      <c r="BF34" t="n">
+        <v>24014</v>
+      </c>
+      <c r="BG34" t="n">
+        <v>24625</v>
+      </c>
+      <c r="BH34" t="n">
+        <v>24903</v>
+      </c>
+      <c r="BI34" t="n">
+        <v>25638</v>
+      </c>
+      <c r="BJ34" t="n">
+        <v>25986</v>
+      </c>
+      <c r="BK34" t="n">
+        <v>26587</v>
+      </c>
+      <c r="BL34" t="n">
+        <v>26937</v>
+      </c>
+      <c r="BM34" t="n">
+        <v>27211</v>
+      </c>
+      <c r="BN34" t="n">
+        <v>27992</v>
+      </c>
+      <c r="BO34" t="n">
+        <v>28090</v>
+      </c>
+      <c r="BP34" t="n">
+        <v>28506</v>
+      </c>
+      <c r="BQ34" t="n">
+        <v>29293</v>
+      </c>
+      <c r="BR34" t="n">
+        <v>30000</v>
+      </c>
+      <c r="BS34" t="n">
+        <v>30596</v>
+      </c>
+      <c r="BT34" t="n">
+        <v>31417</v>
+      </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>1065</v>
-      </c>
-      <c r="B34" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>1397</v>
+      </c>
+      <c r="B35" t="inlineStr">
         <is>
           <t>rautsi__</t>
         </is>
       </c>
-      <c r="C34" t="n">
+      <c r="C35" t="n">
         <v>1</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D35" t="n">
         <v>56</v>
       </c>
-      <c r="E34" t="n">
+      <c r="E35" t="n">
         <v>102</v>
       </c>
-      <c r="F34" t="n">
+      <c r="F35" t="n">
         <v>352</v>
       </c>
-      <c r="G34" t="n">
+      <c r="G35" t="n">
         <v>465</v>
       </c>
-      <c r="H34" t="n">
+      <c r="H35" t="n">
         <v>586</v>
       </c>
-      <c r="I34" t="n">
+      <c r="I35" t="n">
         <v>800</v>
       </c>
-      <c r="J34" t="n">
+      <c r="J35" t="n">
         <v>822</v>
       </c>
-      <c r="K34" t="n">
+      <c r="K35" t="n">
         <v>957</v>
       </c>
-      <c r="L34" t="n">
+      <c r="L35" t="n">
         <v>1033</v>
       </c>
-      <c r="M34" t="n">
+      <c r="M35" t="n">
         <v>1404</v>
       </c>
-      <c r="N34" t="n">
+      <c r="N35" t="n">
         <v>1464</v>
       </c>
-      <c r="O34" t="n">
+      <c r="O35" t="n">
         <v>1510</v>
       </c>
-      <c r="P34" t="n">
+      <c r="P35" t="n">
         <v>1510</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="Q35" t="n">
         <v>1510</v>
       </c>
-      <c r="R34" t="n">
+      <c r="R35" t="n">
         <v>1510</v>
       </c>
-      <c r="S34" t="n">
+      <c r="S35" t="n">
         <v>1648</v>
       </c>
-      <c r="T34" t="n">
+      <c r="T35" t="n">
         <v>1648</v>
       </c>
-      <c r="U34" t="n">
+      <c r="U35" t="n">
         <v>1648</v>
       </c>
-      <c r="V34" t="n">
+      <c r="V35" t="n">
         <v>1648</v>
       </c>
-      <c r="W34" t="n">
+      <c r="W35" t="n">
         <v>1648</v>
       </c>
-      <c r="X34" t="n">
+      <c r="X35" t="n">
         <v>1648</v>
       </c>
-      <c r="Y34" t="n">
+      <c r="Y35" t="n">
         <v>1755</v>
       </c>
-      <c r="Z34" t="n">
+      <c r="Z35" t="n">
         <v>2121</v>
       </c>
-      <c r="AA34" t="n">
+      <c r="AA35" t="n">
         <v>2121</v>
       </c>
-      <c r="AB34" t="n">
+      <c r="AB35" t="n">
         <v>2236</v>
       </c>
-      <c r="AC34" t="n">
+      <c r="AC35" t="n">
         <v>2478</v>
       </c>
-      <c r="AD34" t="n">
+      <c r="AD35" t="n">
         <v>2478</v>
       </c>
-      <c r="AE34" t="n">
+      <c r="AE35" t="n">
         <v>2480</v>
       </c>
-      <c r="AF34" t="n">
+      <c r="AF35" t="n">
         <v>2523</v>
       </c>
-      <c r="AG34" t="n">
+      <c r="AG35" t="n">
         <v>2601</v>
       </c>
-      <c r="AH34" t="n">
+      <c r="AH35" t="n">
         <v>2602</v>
       </c>
-      <c r="AI34" t="n">
+      <c r="AI35" t="n">
         <v>2750</v>
       </c>
-      <c r="AJ34" t="n">
+      <c r="AJ35" t="n">
         <v>2750</v>
       </c>
-      <c r="AK34" t="n">
+      <c r="AK35" t="n">
         <v>2750</v>
       </c>
-      <c r="AL34" t="n">
+      <c r="AL35" t="n">
         <v>2750</v>
       </c>
-      <c r="AM34" t="n">
+      <c r="AM35" t="n">
         <v>2750</v>
       </c>
-      <c r="AN34" t="n">
+      <c r="AN35" t="n">
         <v>2753</v>
       </c>
-      <c r="AO34" t="n">
+      <c r="AO35" t="n">
         <v>2816</v>
       </c>
-      <c r="AP34" t="n">
+      <c r="AP35" t="n">
         <v>2816</v>
       </c>
-      <c r="AQ34" t="n">
+      <c r="AQ35" t="n">
         <v>2816</v>
       </c>
-      <c r="AR34" t="n">
+      <c r="AR35" t="n">
         <v>2816</v>
       </c>
-      <c r="AS34" t="n">
+      <c r="AS35" t="n">
         <v>2816</v>
       </c>
-      <c r="AT34" t="n">
+      <c r="AT35" t="n">
         <v>2854</v>
       </c>
-      <c r="AU34" t="n">
+      <c r="AU35" t="n">
         <v>3129</v>
       </c>
-      <c r="AV34" t="n">
+      <c r="AV35" t="n">
         <v>3154</v>
       </c>
-      <c r="AW34" t="n">
+      <c r="AW35" t="n">
         <v>3200</v>
       </c>
-      <c r="AX34" t="n">
+      <c r="AX35" t="n">
         <v>3219</v>
       </c>
-      <c r="AY34" t="n">
+      <c r="AY35" t="n">
         <v>3219</v>
       </c>
-      <c r="AZ34" t="n">
+      <c r="AZ35" t="n">
         <v>3518</v>
       </c>
-      <c r="BA34" t="n">
+      <c r="BA35" t="n">
         <v>3739</v>
       </c>
-      <c r="BB34" t="n">
+      <c r="BB35" t="n">
         <v>3853</v>
       </c>
-      <c r="BC34" t="n">
+      <c r="BC35" t="n">
         <v>3878</v>
       </c>
+      <c r="BD35" t="n">
+        <v>3956</v>
+      </c>
+      <c r="BE35" t="n">
+        <v>4031</v>
+      </c>
+      <c r="BF35" t="n">
+        <v>4033</v>
+      </c>
+      <c r="BG35" t="n">
+        <v>4079</v>
+      </c>
+      <c r="BH35" t="n">
+        <v>4079</v>
+      </c>
+      <c r="BI35" t="n">
+        <v>4097</v>
+      </c>
+      <c r="BJ35" t="n">
+        <v>4113</v>
+      </c>
+      <c r="BK35" t="n">
+        <v>4137</v>
+      </c>
+      <c r="BL35" t="n">
+        <v>4137</v>
+      </c>
+      <c r="BM35" t="n">
+        <v>4137</v>
+      </c>
+      <c r="BN35" t="n">
+        <v>4525</v>
+      </c>
+      <c r="BO35" t="n">
+        <v>4547</v>
+      </c>
+      <c r="BP35" t="n">
+        <v>4590</v>
+      </c>
+      <c r="BQ35" t="n">
+        <v>4798</v>
+      </c>
+      <c r="BR35" t="n">
+        <v>4819</v>
+      </c>
+      <c r="BS35" t="n">
+        <v>4878</v>
+      </c>
+      <c r="BT35" t="n">
+        <v>4941</v>
+      </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>1170</v>
-      </c>
-      <c r="B35" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>1542</v>
+      </c>
+      <c r="B36" t="inlineStr">
         <is>
           <t>teavapiti</t>
         </is>
       </c>
-      <c r="C35" t="n">
+      <c r="C36" t="n">
         <v>10</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D36" t="n">
         <v>34</v>
       </c>
-      <c r="E35" t="n">
+      <c r="E36" t="n">
         <v>52</v>
       </c>
-      <c r="F35" t="n">
+      <c r="F36" t="n">
         <v>99</v>
       </c>
-      <c r="G35" t="n">
+      <c r="G36" t="n">
         <v>132</v>
       </c>
-      <c r="H35" t="n">
+      <c r="H36" t="n">
         <v>206</v>
       </c>
-      <c r="I35" t="n">
+      <c r="I36" t="n">
         <v>425</v>
       </c>
-      <c r="J35" t="n">
+      <c r="J36" t="n">
         <v>525</v>
       </c>
-      <c r="K35" t="n">
+      <c r="K36" t="n">
         <v>698</v>
       </c>
-      <c r="L35" t="n">
+      <c r="L36" t="n">
         <v>734</v>
       </c>
-      <c r="M35" t="n">
+      <c r="M36" t="n">
         <v>763</v>
       </c>
-      <c r="N35" t="n">
+      <c r="N36" t="n">
         <v>801</v>
       </c>
-      <c r="O35" t="n">
+      <c r="O36" t="n">
         <v>808</v>
       </c>
-      <c r="P35" t="n">
+      <c r="P36" t="n">
         <v>838</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="Q36" t="n">
         <v>963</v>
       </c>
-      <c r="R35" t="n">
+      <c r="R36" t="n">
         <v>1010</v>
       </c>
-      <c r="S35" t="n">
+      <c r="S36" t="n">
         <v>1129</v>
       </c>
-      <c r="T35" t="n">
+      <c r="T36" t="n">
         <v>1268</v>
       </c>
-      <c r="U35" t="n">
+      <c r="U36" t="n">
         <v>1500</v>
       </c>
-      <c r="V35" t="n">
+      <c r="V36" t="n">
         <v>1629</v>
       </c>
-      <c r="W35" t="n">
+      <c r="W36" t="n">
         <v>1682</v>
       </c>
-      <c r="X35" t="n">
+      <c r="X36" t="n">
         <v>1734</v>
       </c>
-      <c r="Y35" t="n">
+      <c r="Y36" t="n">
         <v>1760</v>
       </c>
-      <c r="Z35" t="n">
+      <c r="Z36" t="n">
         <v>1854</v>
       </c>
-      <c r="AA35" t="n">
+      <c r="AA36" t="n">
         <v>1957</v>
       </c>
-      <c r="AB35" t="n">
+      <c r="AB36" t="n">
         <v>2015</v>
       </c>
-      <c r="AC35" t="n">
+      <c r="AC36" t="n">
         <v>2061</v>
       </c>
-      <c r="AD35" t="n">
+      <c r="AD36" t="n">
         <v>2091</v>
       </c>
-      <c r="AE35" t="n">
+      <c r="AE36" t="n">
         <v>2118</v>
       </c>
-      <c r="AF35" t="n">
+      <c r="AF36" t="n">
         <v>2118</v>
       </c>
-      <c r="AG35" t="n">
+      <c r="AG36" t="n">
         <v>2161</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AH36" t="n">
         <v>2178</v>
       </c>
-      <c r="AI35" t="n">
+      <c r="AI36" t="n">
         <v>2295</v>
       </c>
-      <c r="AJ35" t="n">
+      <c r="AJ36" t="n">
         <v>2417</v>
       </c>
-      <c r="AK35" t="n">
+      <c r="AK36" t="n">
         <v>2449</v>
       </c>
-      <c r="AL35" t="n">
+      <c r="AL36" t="n">
         <v>2460</v>
       </c>
-      <c r="AM35" t="n">
+      <c r="AM36" t="n">
         <v>2480</v>
       </c>
-      <c r="AN35" t="n">
+      <c r="AN36" t="n">
         <v>2504</v>
       </c>
-      <c r="AO35" t="n">
+      <c r="AO36" t="n">
         <v>2511</v>
       </c>
-      <c r="AP35" t="n">
+      <c r="AP36" t="n">
         <v>2516</v>
       </c>
-      <c r="AQ35" t="n">
+      <c r="AQ36" t="n">
         <v>2542</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AR36" t="n">
         <v>2571</v>
       </c>
-      <c r="AS35" t="n">
+      <c r="AS36" t="n">
         <v>2622</v>
       </c>
-      <c r="AT35" t="n">
+      <c r="AT36" t="n">
         <v>2662</v>
       </c>
-      <c r="AU35" t="n">
+      <c r="AU36" t="n">
         <v>2690</v>
       </c>
-      <c r="AV35" t="n">
+      <c r="AV36" t="n">
         <v>2707</v>
       </c>
-      <c r="AW35" t="n">
+      <c r="AW36" t="n">
         <v>2837</v>
       </c>
-      <c r="AX35" t="n">
+      <c r="AX36" t="n">
         <v>2982</v>
       </c>
-      <c r="AY35" t="n">
+      <c r="AY36" t="n">
         <v>3032</v>
       </c>
-      <c r="AZ35" t="n">
+      <c r="AZ36" t="n">
         <v>3125</v>
       </c>
-      <c r="BA35" t="n">
+      <c r="BA36" t="n">
         <v>3216</v>
       </c>
-      <c r="BB35" t="n">
+      <c r="BB36" t="n">
         <v>3336</v>
       </c>
-      <c r="BC35" t="n">
+      <c r="BC36" t="n">
         <v>3450</v>
       </c>
+      <c r="BD36" t="n">
+        <v>3562</v>
+      </c>
+      <c r="BE36" t="n">
+        <v>3572</v>
+      </c>
+      <c r="BF36" t="n">
+        <v>3632</v>
+      </c>
+      <c r="BG36" t="n">
+        <v>3667</v>
+      </c>
+      <c r="BH36" t="n">
+        <v>3701</v>
+      </c>
+      <c r="BI36" t="n">
+        <v>3806</v>
+      </c>
+      <c r="BJ36" t="n">
+        <v>3880</v>
+      </c>
+      <c r="BK36" t="n">
+        <v>3990</v>
+      </c>
+      <c r="BL36" t="n">
+        <v>4049</v>
+      </c>
+      <c r="BM36" t="n">
+        <v>4134</v>
+      </c>
+      <c r="BN36" t="n">
+        <v>4175</v>
+      </c>
+      <c r="BO36" t="n">
+        <v>4227</v>
+      </c>
+      <c r="BP36" t="n">
+        <v>4232</v>
+      </c>
+      <c r="BQ36" t="n">
+        <v>4302</v>
+      </c>
+      <c r="BR36" t="n">
+        <v>4420</v>
+      </c>
+      <c r="BS36" t="n">
+        <v>4486</v>
+      </c>
+      <c r="BT36" t="n">
+        <v>4575</v>
+      </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>1181</v>
-      </c>
-      <c r="B36" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>1557</v>
+      </c>
+      <c r="B37" t="inlineStr">
         <is>
           <t>theluvros</t>
         </is>
       </c>
-      <c r="C36" t="n">
+      <c r="C37" t="n">
         <v>51</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D37" t="n">
         <v>51</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E37" t="n">
         <v>51</v>
       </c>
-      <c r="F36" t="n">
+      <c r="F37" t="n">
         <v>51</v>
       </c>
-      <c r="G36" t="n">
+      <c r="G37" t="n">
         <v>51</v>
       </c>
-      <c r="H36" t="n">
+      <c r="H37" t="n">
         <v>51</v>
       </c>
-      <c r="I36" t="n">
+      <c r="I37" t="n">
         <v>51</v>
       </c>
-      <c r="J36" t="n">
+      <c r="J37" t="n">
         <v>51</v>
       </c>
-      <c r="K36" t="n">
+      <c r="K37" t="n">
         <v>51</v>
       </c>
-      <c r="L36" t="n">
+      <c r="L37" t="n">
         <v>51</v>
       </c>
-      <c r="M36" t="n">
+      <c r="M37" t="n">
         <v>51</v>
       </c>
-      <c r="N36" t="n">
+      <c r="N37" t="n">
         <v>51</v>
       </c>
-      <c r="O36" t="n">
+      <c r="O37" t="n">
         <v>51</v>
       </c>
-      <c r="P36" t="n">
+      <c r="P37" t="n">
         <v>51</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="Q37" t="n">
         <v>51</v>
       </c>
-      <c r="R36" t="n">
+      <c r="R37" t="n">
         <v>51</v>
       </c>
-      <c r="S36" t="n">
+      <c r="S37" t="n">
         <v>51</v>
       </c>
-      <c r="T36" t="n">
+      <c r="T37" t="n">
         <v>51</v>
       </c>
-      <c r="U36" t="n">
+      <c r="U37" t="n">
         <v>51</v>
       </c>
-      <c r="V36" t="n">
+      <c r="V37" t="n">
         <v>51</v>
       </c>
-      <c r="W36" t="n">
+      <c r="W37" t="n">
         <v>51</v>
       </c>
-      <c r="X36" t="n">
+      <c r="X37" t="n">
         <v>51</v>
       </c>
-      <c r="Y36" t="n">
+      <c r="Y37" t="n">
         <v>51</v>
       </c>
-      <c r="Z36" t="n">
+      <c r="Z37" t="n">
         <v>51</v>
       </c>
-      <c r="AA36" t="n">
+      <c r="AA37" t="n">
         <v>51</v>
       </c>
-      <c r="AB36" t="n">
+      <c r="AB37" t="n">
         <v>51</v>
       </c>
-      <c r="AC36" t="n">
+      <c r="AC37" t="n">
         <v>51</v>
       </c>
-      <c r="AD36" t="n">
+      <c r="AD37" t="n">
         <v>51</v>
       </c>
-      <c r="AE36" t="n">
+      <c r="AE37" t="n">
         <v>51</v>
       </c>
-      <c r="AF36" t="n">
+      <c r="AF37" t="n">
         <v>51</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AG37" t="n">
         <v>51</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AH37" t="n">
         <v>51</v>
       </c>
-      <c r="AI36" t="n">
+      <c r="AI37" t="n">
         <v>51</v>
       </c>
-      <c r="AJ36" t="n">
+      <c r="AJ37" t="n">
         <v>51</v>
       </c>
-      <c r="AK36" t="n">
+      <c r="AK37" t="n">
         <v>51</v>
       </c>
-      <c r="AL36" t="n">
+      <c r="AL37" t="n">
         <v>51</v>
       </c>
-      <c r="AM36" t="n">
+      <c r="AM37" t="n">
         <v>51</v>
       </c>
-      <c r="AN36" t="n">
+      <c r="AN37" t="n">
         <v>51</v>
       </c>
-      <c r="AO36" t="n">
+      <c r="AO37" t="n">
         <v>51</v>
       </c>
-      <c r="AP36" t="n">
+      <c r="AP37" t="n">
         <v>51</v>
       </c>
-      <c r="AQ36" t="n">
+      <c r="AQ37" t="n">
         <v>51</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AR37" t="n">
         <v>51</v>
       </c>
-      <c r="AS36" t="n">
+      <c r="AS37" t="n">
         <v>51</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AT37" t="n">
         <v>51</v>
       </c>
-      <c r="AU36" t="n">
+      <c r="AU37" t="n">
         <v>51</v>
       </c>
-      <c r="AV36" t="n">
+      <c r="AV37" t="n">
         <v>51</v>
       </c>
-      <c r="AW36" t="n">
+      <c r="AW37" t="n">
         <v>51</v>
       </c>
-      <c r="AX36" t="n">
+      <c r="AX37" t="n">
         <v>51</v>
       </c>
-      <c r="AY36" t="n">
+      <c r="AY37" t="n">
         <v>51</v>
       </c>
-      <c r="AZ36" t="n">
+      <c r="AZ37" t="n">
         <v>51</v>
       </c>
-      <c r="BA36" t="n">
+      <c r="BA37" t="n">
         <v>51</v>
       </c>
-      <c r="BB36" t="n">
+      <c r="BB37" t="n">
         <v>51</v>
       </c>
-      <c r="BC36" t="n">
+      <c r="BC37" t="n">
         <v>51</v>
       </c>
+      <c r="BD37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BE37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BF37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BG37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BH37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BI37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BJ37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BK37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BL37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BM37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BN37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BO37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BP37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BQ37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BR37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BS37" t="n">
+        <v>51</v>
+      </c>
+      <c r="BT37" t="n">
+        <v>51</v>
+      </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>1267</v>
-      </c>
-      <c r="B37" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>1678</v>
+      </c>
+      <c r="B38" t="inlineStr">
         <is>
           <t>yop2u</t>
         </is>
       </c>
-      <c r="C37" t="n">
+      <c r="C38" t="n">
         <v>49</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D38" t="n">
         <v>132</v>
       </c>
-      <c r="E37" t="n">
+      <c r="E38" t="n">
         <v>135</v>
       </c>
-      <c r="F37" t="n">
+      <c r="F38" t="n">
         <v>157</v>
       </c>
-      <c r="G37" t="n">
+      <c r="G38" t="n">
         <v>180</v>
       </c>
-      <c r="H37" t="n">
+      <c r="H38" t="n">
         <v>186</v>
       </c>
-      <c r="I37" t="n">
+      <c r="I38" t="n">
         <v>286</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J38" t="n">
         <v>288</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K38" t="n">
         <v>289</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L38" t="n">
         <v>289</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M38" t="n">
         <v>293</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N38" t="n">
         <v>293</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O38" t="n">
         <v>293</v>
       </c>
-      <c r="P37" t="n">
+      <c r="P38" t="n">
         <v>367</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="Q38" t="n">
         <v>386</v>
       </c>
-      <c r="R37" t="n">
+      <c r="R38" t="n">
         <v>405</v>
       </c>
-      <c r="S37" t="n">
+      <c r="S38" t="n">
         <v>454</v>
       </c>
-      <c r="T37" t="n">
+      <c r="T38" t="n">
         <v>462</v>
       </c>
-      <c r="U37" t="n">
+      <c r="U38" t="n">
         <v>477</v>
       </c>
-      <c r="V37" t="n">
+      <c r="V38" t="n">
         <v>516</v>
       </c>
-      <c r="W37" t="n">
+      <c r="W38" t="n">
         <v>529</v>
       </c>
-      <c r="X37" t="n">
+      <c r="X38" t="n">
         <v>541</v>
       </c>
-      <c r="Y37" t="n">
+      <c r="Y38" t="n">
         <v>547</v>
       </c>
-      <c r="Z37" t="n">
+      <c r="Z38" t="n">
         <v>557</v>
       </c>
-      <c r="AA37" t="n">
+      <c r="AA38" t="n">
         <v>564</v>
       </c>
-      <c r="AB37" t="n">
+      <c r="AB38" t="n">
         <v>568</v>
       </c>
-      <c r="AC37" t="n">
+      <c r="AC38" t="n">
         <v>573</v>
       </c>
-      <c r="AD37" t="n">
+      <c r="AD38" t="n">
         <v>580</v>
       </c>
-      <c r="AE37" t="n">
+      <c r="AE38" t="n">
         <v>587</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AF38" t="n">
         <v>587</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AG38" t="n">
         <v>591</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AH38" t="n">
         <v>592</v>
       </c>
-      <c r="AI37" t="n">
+      <c r="AI38" t="n">
         <v>592</v>
       </c>
-      <c r="AJ37" t="n">
+      <c r="AJ38" t="n">
         <v>592</v>
       </c>
-      <c r="AK37" t="n">
+      <c r="AK38" t="n">
         <v>594</v>
       </c>
-      <c r="AL37" t="n">
+      <c r="AL38" t="n">
         <v>594</v>
       </c>
-      <c r="AM37" t="n">
+      <c r="AM38" t="n">
         <v>595</v>
       </c>
-      <c r="AN37" t="n">
+      <c r="AN38" t="n">
         <v>597</v>
       </c>
-      <c r="AO37" t="n">
+      <c r="AO38" t="n">
         <v>600</v>
       </c>
-      <c r="AP37" t="n">
+      <c r="AP38" t="n">
         <v>603</v>
       </c>
-      <c r="AQ37" t="n">
+      <c r="AQ38" t="n">
         <v>609</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AR38" t="n">
         <v>611</v>
       </c>
-      <c r="AS37" t="n">
+      <c r="AS38" t="n">
         <v>615</v>
       </c>
-      <c r="AT37" t="n">
+      <c r="AT38" t="n">
         <v>616</v>
       </c>
-      <c r="AU37" t="n">
+      <c r="AU38" t="n">
         <v>620</v>
       </c>
-      <c r="AV37" t="n">
+      <c r="AV38" t="n">
         <v>623</v>
       </c>
-      <c r="AW37" t="n">
+      <c r="AW38" t="n">
         <v>625</v>
       </c>
-      <c r="AX37" t="n">
+      <c r="AX38" t="n">
         <v>625</v>
       </c>
-      <c r="AY37" t="n">
+      <c r="AY38" t="n">
         <v>676</v>
       </c>
-      <c r="AZ37" t="n">
+      <c r="AZ38" t="n">
         <v>676</v>
       </c>
-      <c r="BA37" t="n">
+      <c r="BA38" t="n">
         <v>676</v>
       </c>
-      <c r="BB37" t="n">
+      <c r="BB38" t="n">
         <v>676</v>
       </c>
-      <c r="BC37" t="n">
+      <c r="BC38" t="n">
         <v>677</v>
       </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>1272</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>yrgakhosoo</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" t="n">
-        <v>0</v>
-      </c>
-      <c r="J38" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0</v>
-      </c>
-      <c r="P38" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1</v>
-      </c>
-      <c r="S38" t="n">
-        <v>1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1</v>
-      </c>
-      <c r="U38" t="n">
-        <v>6</v>
-      </c>
-      <c r="V38" t="n">
-        <v>6</v>
-      </c>
-      <c r="W38" t="n">
-        <v>13</v>
-      </c>
-      <c r="X38" t="n">
-        <v>21</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>21</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>24</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>28</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>28</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>28</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>28</v>
-      </c>
-      <c r="BC38" t="n">
-        <v>28</v>
+      <c r="BD38" t="n">
+        <v>677</v>
+      </c>
+      <c r="BE38" t="n">
+        <v>677</v>
+      </c>
+      <c r="BF38" t="n">
+        <v>682</v>
+      </c>
+      <c r="BG38" t="n">
+        <v>686</v>
+      </c>
+      <c r="BH38" t="n">
+        <v>704</v>
+      </c>
+      <c r="BI38" t="n">
+        <v>709</v>
+      </c>
+      <c r="BJ38" t="n">
+        <v>722</v>
+      </c>
+      <c r="BK38" t="n">
+        <v>744</v>
+      </c>
+      <c r="BL38" t="n">
+        <v>756</v>
+      </c>
+      <c r="BM38" t="n">
+        <v>761</v>
+      </c>
+      <c r="BN38" t="n">
+        <v>762</v>
+      </c>
+      <c r="BO38" t="n">
+        <v>762</v>
+      </c>
+      <c r="BP38" t="n">
+        <v>762</v>
+      </c>
+      <c r="BQ38" t="n">
+        <v>764</v>
+      </c>
+      <c r="BR38" t="n">
+        <v>764</v>
+      </c>
+      <c r="BS38" t="n">
+        <v>764</v>
+      </c>
+      <c r="BT38" t="n">
+        <v>764</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>1273</v>
+        <v>1690</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>yupbekha</t>
+          <t>zeil</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="E39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AD39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AI39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AJ39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AK39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AL39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AM39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AN39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AO39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AP39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AQ39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AR39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AS39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AT39" t="n">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="AU39" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AV39" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AW39" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AX39" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AY39" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="AZ39" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="BA39" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="BB39" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="BC39" t="n">
-        <v>47</v>
+        <v>26</v>
+      </c>
+      <c r="BD39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BF39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BG39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BH39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BI39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BJ39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BK39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BL39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BM39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BN39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BO39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BP39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BQ39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BR39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BS39" t="n">
+        <v>26</v>
+      </c>
+      <c r="BT39" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>1274</v>
+        <v>1691</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>zKermel</t>
+          <t>zen0_sama_senpai</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -7050,154 +9039,205 @@
         <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB40" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="AC40" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="AD40" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="AE40" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="AF40" t="n">
-        <v>50</v>
+        <v>11</v>
       </c>
       <c r="AG40" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="AH40" t="n">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="AI40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AJ40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AK40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AL40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AM40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AN40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AO40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AP40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AQ40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AR40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AS40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AT40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AU40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AV40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AW40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AX40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AY40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="AZ40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="BA40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="BB40" t="n">
-        <v>53</v>
+        <v>12</v>
       </c>
       <c r="BC40" t="n">
-        <v>53</v>
+        <v>12</v>
+      </c>
+      <c r="BD40" t="n">
+        <v>12</v>
+      </c>
+      <c r="BE40" t="n">
+        <v>20</v>
+      </c>
+      <c r="BF40" t="n">
+        <v>20</v>
+      </c>
+      <c r="BG40" t="n">
+        <v>20</v>
+      </c>
+      <c r="BH40" t="n">
+        <v>20</v>
+      </c>
+      <c r="BI40" t="n">
+        <v>20</v>
+      </c>
+      <c r="BJ40" t="n">
+        <v>20</v>
+      </c>
+      <c r="BK40" t="n">
+        <v>20</v>
+      </c>
+      <c r="BL40" t="n">
+        <v>21</v>
+      </c>
+      <c r="BM40" t="n">
+        <v>21</v>
+      </c>
+      <c r="BN40" t="n">
+        <v>30</v>
+      </c>
+      <c r="BO40" t="n">
+        <v>30</v>
+      </c>
+      <c r="BP40" t="n">
+        <v>30</v>
+      </c>
+      <c r="BQ40" t="n">
+        <v>30</v>
+      </c>
+      <c r="BR40" t="n">
+        <v>30</v>
+      </c>
+      <c r="BS40" t="n">
+        <v>30</v>
+      </c>
+      <c r="BT40" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>1275</v>
+        <v>1692</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>zakflash</t>
+          <t>zenjuryx</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -7222,489 +9262,642 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="Z41" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="AA41" t="n">
-        <v>1</v>
+        <v>40</v>
       </c>
       <c r="AB41" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="AC41" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AD41" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AE41" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="AF41" t="n">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="AG41" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="AH41" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AI41" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AJ41" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="AK41" t="n">
-        <v>64</v>
+        <v>40</v>
       </c>
       <c r="AL41" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="AM41" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="AN41" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="AO41" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="AP41" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="AQ41" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="AR41" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="AS41" t="n">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="AT41" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AU41" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AV41" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AW41" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AX41" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AY41" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="AZ41" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="BA41" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="BB41" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="BC41" t="n">
-        <v>71</v>
+        <v>40</v>
+      </c>
+      <c r="BD41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BI41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BJ41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BK41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BL41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BM41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BP41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BR41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS41" t="n">
+        <v>40</v>
+      </c>
+      <c r="BT41" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>1276</v>
+        <v>1693</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>zeil</t>
+          <t>zequifu</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G42" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R42" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="S42" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T42" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="U42" t="n">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="V42" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="W42" t="n">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="X42" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="Y42" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="Z42" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="AA42" t="n">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="AB42" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="AC42" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="AD42" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="AE42" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="AF42" t="n">
-        <v>23</v>
+        <v>72</v>
       </c>
       <c r="AG42" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="AH42" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="AI42" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="AJ42" t="n">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="AK42" t="n">
-        <v>23</v>
+        <v>81</v>
       </c>
       <c r="AL42" t="n">
-        <v>23</v>
+        <v>83</v>
       </c>
       <c r="AM42" t="n">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="AN42" t="n">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="AO42" t="n">
-        <v>23</v>
+        <v>87</v>
       </c>
       <c r="AP42" t="n">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="AQ42" t="n">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="AR42" t="n">
-        <v>23</v>
+        <v>89</v>
       </c>
       <c r="AS42" t="n">
-        <v>23</v>
+        <v>91</v>
       </c>
       <c r="AT42" t="n">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="AU42" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="AV42" t="n">
-        <v>24</v>
+        <v>96</v>
       </c>
       <c r="AW42" t="n">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="AX42" t="n">
-        <v>24</v>
+        <v>102</v>
       </c>
       <c r="AY42" t="n">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="AZ42" t="n">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="BA42" t="n">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="BB42" t="n">
-        <v>26</v>
+        <v>103</v>
       </c>
       <c r="BC42" t="n">
-        <v>26</v>
+        <v>103</v>
+      </c>
+      <c r="BD42" t="n">
+        <v>104</v>
+      </c>
+      <c r="BE42" t="n">
+        <v>104</v>
+      </c>
+      <c r="BF42" t="n">
+        <v>105</v>
+      </c>
+      <c r="BG42" t="n">
+        <v>105</v>
+      </c>
+      <c r="BH42" t="n">
+        <v>105</v>
+      </c>
+      <c r="BI42" t="n">
+        <v>109</v>
+      </c>
+      <c r="BJ42" t="n">
+        <v>109</v>
+      </c>
+      <c r="BK42" t="n">
+        <v>110</v>
+      </c>
+      <c r="BL42" t="n">
+        <v>112</v>
+      </c>
+      <c r="BM42" t="n">
+        <v>112</v>
+      </c>
+      <c r="BN42" t="n">
+        <v>112</v>
+      </c>
+      <c r="BO42" t="n">
+        <v>113</v>
+      </c>
+      <c r="BP42" t="n">
+        <v>114</v>
+      </c>
+      <c r="BQ42" t="n">
+        <v>115</v>
+      </c>
+      <c r="BR42" t="n">
+        <v>115</v>
+      </c>
+      <c r="BS42" t="n">
+        <v>115</v>
+      </c>
+      <c r="BT42" t="n">
+        <v>115</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>1277</v>
+        <v>1694</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>zenjuryx</t>
+          <t>zerg_zerg_</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="J43" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="K43" t="n">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L43" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="M43" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="N43" t="n">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="O43" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="P43" t="n">
-        <v>12</v>
+        <v>52</v>
       </c>
       <c r="Q43" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="R43" t="n">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c r="S43" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="T43" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="U43" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="V43" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="W43" t="n">
-        <v>40</v>
+        <v>77</v>
       </c>
       <c r="X43" t="n">
-        <v>40</v>
+        <v>87</v>
       </c>
       <c r="Y43" t="n">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="Z43" t="n">
-        <v>40</v>
+        <v>117</v>
       </c>
       <c r="AA43" t="n">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AB43" t="n">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AC43" t="n">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AD43" t="n">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AE43" t="n">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AF43" t="n">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AG43" t="n">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c r="AH43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AI43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AJ43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AK43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AL43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AM43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AN43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AO43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AP43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AQ43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AR43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AS43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AT43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AU43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AV43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AW43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AX43" t="n">
-        <v>40</v>
+        <v>129</v>
       </c>
       <c r="AY43" t="n">
-        <v>40</v>
+        <v>131</v>
       </c>
       <c r="AZ43" t="n">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="BA43" t="n">
-        <v>40</v>
+        <v>133</v>
       </c>
       <c r="BB43" t="n">
-        <v>40</v>
+        <v>136</v>
       </c>
       <c r="BC43" t="n">
-        <v>40</v>
+        <v>136</v>
+      </c>
+      <c r="BD43" t="n">
+        <v>147</v>
+      </c>
+      <c r="BE43" t="n">
+        <v>147</v>
+      </c>
+      <c r="BF43" t="n">
+        <v>147</v>
+      </c>
+      <c r="BG43" t="n">
+        <v>147</v>
+      </c>
+      <c r="BH43" t="n">
+        <v>147</v>
+      </c>
+      <c r="BI43" t="n">
+        <v>147</v>
+      </c>
+      <c r="BJ43" t="n">
+        <v>147</v>
+      </c>
+      <c r="BK43" t="n">
+        <v>147</v>
+      </c>
+      <c r="BL43" t="n">
+        <v>147</v>
+      </c>
+      <c r="BM43" t="n">
+        <v>147</v>
+      </c>
+      <c r="BN43" t="n">
+        <v>153</v>
+      </c>
+      <c r="BO43" t="n">
+        <v>153</v>
+      </c>
+      <c r="BP43" t="n">
+        <v>153</v>
+      </c>
+      <c r="BQ43" t="n">
+        <v>173</v>
+      </c>
+      <c r="BR43" t="n">
+        <v>245</v>
+      </c>
+      <c r="BS43" t="n">
+        <v>245</v>
+      </c>
+      <c r="BT43" t="n">
+        <v>253</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>1278</v>
+        <v>1695</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>zequifu</t>
+          <t>ziico13</t>
         </is>
       </c>
       <c r="C44" t="n">
@@ -7741,308 +9934,410 @@
         <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P44" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q44" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="R44" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T44" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="U44" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="V44" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="W44" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="X44" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Y44" t="n">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="Z44" t="n">
-        <v>51</v>
+        <v>29</v>
       </c>
       <c r="AA44" t="n">
-        <v>62</v>
+        <v>30</v>
       </c>
       <c r="AB44" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="AC44" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="AD44" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="AE44" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="AF44" t="n">
-        <v>72</v>
+        <v>31</v>
       </c>
       <c r="AG44" t="n">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="AH44" t="n">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="AI44" t="n">
-        <v>76</v>
+        <v>31</v>
       </c>
       <c r="AJ44" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="AK44" t="n">
-        <v>81</v>
+        <v>31</v>
       </c>
       <c r="AL44" t="n">
-        <v>83</v>
+        <v>31</v>
       </c>
       <c r="AM44" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="AN44" t="n">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="AO44" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="AP44" t="n">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="AQ44" t="n">
-        <v>88</v>
+        <v>31</v>
       </c>
       <c r="AR44" t="n">
-        <v>89</v>
+        <v>31</v>
       </c>
       <c r="AS44" t="n">
-        <v>91</v>
+        <v>31</v>
       </c>
       <c r="AT44" t="n">
-        <v>93</v>
+        <v>31</v>
       </c>
       <c r="AU44" t="n">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="AV44" t="n">
-        <v>96</v>
+        <v>31</v>
       </c>
       <c r="AW44" t="n">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="AX44" t="n">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="AY44" t="n">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="AZ44" t="n">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="BA44" t="n">
-        <v>102</v>
+        <v>31</v>
       </c>
       <c r="BB44" t="n">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="BC44" t="n">
-        <v>103</v>
+        <v>34</v>
+      </c>
+      <c r="BD44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BE44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BF44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BG44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BH44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BI44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BJ44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BK44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BL44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BM44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BN44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BO44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BP44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BQ44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BR44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BS44" t="n">
+        <v>34</v>
+      </c>
+      <c r="BT44" t="n">
+        <v>34</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>1279</v>
+        <v>1696</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>zerg_zerg_</t>
+          <t>zmaauu</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F45" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G45" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="H45" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="K45" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="L45" t="n">
-        <v>48</v>
+        <v>2</v>
       </c>
       <c r="M45" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="N45" t="n">
-        <v>51</v>
+        <v>2</v>
       </c>
       <c r="O45" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="P45" t="n">
-        <v>52</v>
+        <v>2</v>
       </c>
       <c r="Q45" t="n">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="R45" t="n">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="S45" t="n">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
-        <v>76</v>
+        <v>3</v>
       </c>
       <c r="V45" t="n">
-        <v>77</v>
+        <v>3</v>
       </c>
       <c r="W45" t="n">
-        <v>77</v>
+        <v>17</v>
       </c>
       <c r="X45" t="n">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="Y45" t="n">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="Z45" t="n">
-        <v>117</v>
+        <v>18</v>
       </c>
       <c r="AA45" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="AB45" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="AC45" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="AD45" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="AE45" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="AF45" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="AG45" t="n">
-        <v>125</v>
+        <v>18</v>
       </c>
       <c r="AH45" t="n">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AI45" t="n">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AJ45" t="n">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AK45" t="n">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AL45" t="n">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AM45" t="n">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AN45" t="n">
-        <v>129</v>
+        <v>18</v>
       </c>
       <c r="AO45" t="n">
-        <v>129</v>
+        <v>39</v>
       </c>
       <c r="AP45" t="n">
-        <v>129</v>
+        <v>43</v>
       </c>
       <c r="AQ45" t="n">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="AR45" t="n">
-        <v>129</v>
+        <v>44</v>
       </c>
       <c r="AS45" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="AT45" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="AU45" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="AV45" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="AW45" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="AX45" t="n">
-        <v>129</v>
+        <v>45</v>
       </c>
       <c r="AY45" t="n">
-        <v>131</v>
+        <v>45</v>
       </c>
       <c r="AZ45" t="n">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="BA45" t="n">
-        <v>133</v>
+        <v>45</v>
       </c>
       <c r="BB45" t="n">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="BC45" t="n">
-        <v>136</v>
+        <v>45</v>
+      </c>
+      <c r="BD45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BE45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BF45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BG45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BH45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BI45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BJ45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BK45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BL45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BM45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BN45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BO45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BP45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BQ45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BR45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BS45" t="n">
+        <v>45</v>
+      </c>
+      <c r="BT45" t="n">
+        <v>45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>1280</v>
+        <v>1697</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ziico13</t>
+          <t>zmird_</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -8061,157 +10356,208 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="O46" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="P46" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="Q46" t="n">
+        <v>1</v>
+      </c>
+      <c r="R46" t="n">
+        <v>1</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>11</v>
+      </c>
+      <c r="V46" t="n">
+        <v>11</v>
+      </c>
+      <c r="W46" t="n">
+        <v>11</v>
+      </c>
+      <c r="X46" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>11</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>17</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AP46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AQ46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AU46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AV46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AW46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AY46" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ46" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA46" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB46" t="n">
+        <v>18</v>
+      </c>
+      <c r="BC46" t="n">
+        <v>18</v>
+      </c>
+      <c r="BD46" t="n">
+        <v>18</v>
+      </c>
+      <c r="BE46" t="n">
         <v>20</v>
       </c>
-      <c r="R46" t="n">
-        <v>20</v>
-      </c>
-      <c r="S46" t="n">
-        <v>20</v>
-      </c>
-      <c r="T46" t="n">
-        <v>20</v>
-      </c>
-      <c r="U46" t="n">
-        <v>23</v>
-      </c>
-      <c r="V46" t="n">
+      <c r="BF46" t="n">
         <v>28</v>
       </c>
-      <c r="W46" t="n">
+      <c r="BG46" t="n">
         <v>28</v>
       </c>
-      <c r="X46" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>28</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>29</v>
-      </c>
-      <c r="AA46" t="n">
+      <c r="BH46" t="n">
         <v>30</v>
       </c>
-      <c r="AB46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AO46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AP46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AQ46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AR46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AS46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AT46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AU46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AV46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AW46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AX46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AY46" t="n">
-        <v>31</v>
-      </c>
-      <c r="AZ46" t="n">
-        <v>31</v>
-      </c>
-      <c r="BA46" t="n">
-        <v>31</v>
-      </c>
-      <c r="BB46" t="n">
-        <v>31</v>
-      </c>
-      <c r="BC46" t="n">
-        <v>34</v>
+      <c r="BI46" t="n">
+        <v>30</v>
+      </c>
+      <c r="BJ46" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK46" t="n">
+        <v>30</v>
+      </c>
+      <c r="BL46" t="n">
+        <v>36</v>
+      </c>
+      <c r="BM46" t="n">
+        <v>36</v>
+      </c>
+      <c r="BN46" t="n">
+        <v>36</v>
+      </c>
+      <c r="BO46" t="n">
+        <v>36</v>
+      </c>
+      <c r="BP46" t="n">
+        <v>36</v>
+      </c>
+      <c r="BQ46" t="n">
+        <v>36</v>
+      </c>
+      <c r="BR46" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS46" t="n">
+        <v>36</v>
+      </c>
+      <c r="BT46" t="n">
+        <v>36</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>1281</v>
+        <v>1698</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>zmaauu</t>
+          <t>zoffeswe</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -8221,166 +10567,217 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="R47" t="n">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="T47" t="n">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="U47" t="n">
-        <v>3</v>
+        <v>53</v>
       </c>
       <c r="V47" t="n">
-        <v>3</v>
+        <v>54</v>
       </c>
       <c r="W47" t="n">
-        <v>17</v>
+        <v>60</v>
       </c>
       <c r="X47" t="n">
-        <v>17</v>
+        <v>61</v>
       </c>
       <c r="Y47" t="n">
-        <v>18</v>
+        <v>62</v>
       </c>
       <c r="Z47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AA47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AB47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AC47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AD47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AE47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AF47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AG47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AH47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AI47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AJ47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AK47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AL47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AM47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AN47" t="n">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="AO47" t="n">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="AP47" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="AQ47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AR47" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="AS47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="AT47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="AU47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="AV47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="AW47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="AX47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="AY47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="AZ47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="BA47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="BB47" t="n">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="BC47" t="n">
-        <v>45</v>
+        <v>68</v>
+      </c>
+      <c r="BD47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BE47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BF47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BG47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BH47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BI47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BJ47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BK47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BL47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BM47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BN47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BO47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BP47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BQ47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BR47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BS47" t="n">
+        <v>68</v>
+      </c>
+      <c r="BT47" t="n">
+        <v>68</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>1282</v>
+        <v>1699</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>zoffeswe</t>
+          <t>zoro_enma1</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -8420,136 +10817,187 @@
         <v>0</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AE48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AF48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AL48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AO48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AP48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AQ48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AR48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AS48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AT48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AU48" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="AV48" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="AW48" t="n">
-        <v>68</v>
+        <v>96</v>
       </c>
       <c r="AX48" t="n">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="AY48" t="n">
-        <v>68</v>
+        <v>127</v>
       </c>
       <c r="AZ48" t="n">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="BA48" t="n">
-        <v>68</v>
+        <v>129</v>
       </c>
       <c r="BB48" t="n">
-        <v>68</v>
+        <v>134</v>
       </c>
       <c r="BC48" t="n">
-        <v>68</v>
+        <v>134</v>
+      </c>
+      <c r="BD48" t="n">
+        <v>134</v>
+      </c>
+      <c r="BE48" t="n">
+        <v>134</v>
+      </c>
+      <c r="BF48" t="n">
+        <v>134</v>
+      </c>
+      <c r="BG48" t="n">
+        <v>135</v>
+      </c>
+      <c r="BH48" t="n">
+        <v>135</v>
+      </c>
+      <c r="BI48" t="n">
+        <v>135</v>
+      </c>
+      <c r="BJ48" t="n">
+        <v>135</v>
+      </c>
+      <c r="BK48" t="n">
+        <v>135</v>
+      </c>
+      <c r="BL48" t="n">
+        <v>135</v>
+      </c>
+      <c r="BM48" t="n">
+        <v>135</v>
+      </c>
+      <c r="BN48" t="n">
+        <v>135</v>
+      </c>
+      <c r="BO48" t="n">
+        <v>135</v>
+      </c>
+      <c r="BP48" t="n">
+        <v>146</v>
+      </c>
+      <c r="BQ48" t="n">
+        <v>146</v>
+      </c>
+      <c r="BR48" t="n">
+        <v>146</v>
+      </c>
+      <c r="BS48" t="n">
+        <v>146</v>
+      </c>
+      <c r="BT48" t="n">
+        <v>146</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>1283</v>
+        <v>1700</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>zoro_enma1</t>
+          <t>zuccaaa</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -8571,154 +11019,205 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="K49" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>59</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>147</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>154</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>157</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>174</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>194</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>214</v>
       </c>
       <c r="AD49" t="n">
-        <v>0</v>
+        <v>215</v>
       </c>
       <c r="AE49" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>225</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="AK49" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="AL49" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="AO49" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="AP49" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="AQ49" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="AR49" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="AS49" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="AT49" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="AU49" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="AV49" t="n">
-        <v>93</v>
+        <v>248</v>
       </c>
       <c r="AW49" t="n">
-        <v>96</v>
+        <v>248</v>
       </c>
       <c r="AX49" t="n">
-        <v>114</v>
+        <v>248</v>
       </c>
       <c r="AY49" t="n">
-        <v>127</v>
+        <v>248</v>
       </c>
       <c r="AZ49" t="n">
-        <v>128</v>
+        <v>248</v>
       </c>
       <c r="BA49" t="n">
-        <v>129</v>
+        <v>248</v>
       </c>
       <c r="BB49" t="n">
-        <v>134</v>
+        <v>248</v>
       </c>
       <c r="BC49" t="n">
-        <v>134</v>
+        <v>248</v>
+      </c>
+      <c r="BD49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BE49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BF49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BG49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BH49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BI49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BJ49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BK49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BL49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BM49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BN49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BO49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BP49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BQ49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BR49" t="n">
+        <v>248</v>
+      </c>
+      <c r="BS49" t="n">
+        <v>257</v>
+      </c>
+      <c r="BT49" t="n">
+        <v>257</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>1284</v>
+        <v>1701</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>zuccaaa</t>
+          <t>zwiebelbrotlive</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -8740,492 +11239,645 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>55</v>
+        <v>1</v>
       </c>
       <c r="J50" t="n">
-        <v>59</v>
+        <v>2</v>
       </c>
       <c r="K50" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="L50" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="M50" t="n">
-        <v>59</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="O50" t="n">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="P50" t="n">
-        <v>144</v>
+        <v>3</v>
       </c>
       <c r="Q50" t="n">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="R50" t="n">
-        <v>144</v>
+        <v>11</v>
       </c>
       <c r="S50" t="n">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="T50" t="n">
-        <v>144</v>
+        <v>13</v>
       </c>
       <c r="U50" t="n">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="V50" t="n">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="W50" t="n">
-        <v>147</v>
+        <v>13</v>
       </c>
       <c r="X50" t="n">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="Y50" t="n">
-        <v>157</v>
+        <v>13</v>
       </c>
       <c r="Z50" t="n">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="AA50" t="n">
-        <v>174</v>
+        <v>13</v>
       </c>
       <c r="AB50" t="n">
-        <v>194</v>
+        <v>13</v>
       </c>
       <c r="AC50" t="n">
-        <v>214</v>
+        <v>13</v>
       </c>
       <c r="AD50" t="n">
-        <v>215</v>
+        <v>13</v>
       </c>
       <c r="AE50" t="n">
-        <v>219</v>
+        <v>13</v>
       </c>
       <c r="AF50" t="n">
-        <v>225</v>
+        <v>13</v>
       </c>
       <c r="AG50" t="n">
-        <v>229</v>
+        <v>13</v>
       </c>
       <c r="AH50" t="n">
-        <v>229</v>
+        <v>13</v>
       </c>
       <c r="AI50" t="n">
-        <v>230</v>
+        <v>13</v>
       </c>
       <c r="AJ50" t="n">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="AK50" t="n">
-        <v>232</v>
+        <v>13</v>
       </c>
       <c r="AL50" t="n">
-        <v>233</v>
+        <v>13</v>
       </c>
       <c r="AM50" t="n">
-        <v>234</v>
+        <v>13</v>
       </c>
       <c r="AN50" t="n">
-        <v>234</v>
+        <v>13</v>
       </c>
       <c r="AO50" t="n">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="AP50" t="n">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="AQ50" t="n">
-        <v>237</v>
+        <v>27</v>
       </c>
       <c r="AR50" t="n">
-        <v>245</v>
+        <v>27</v>
       </c>
       <c r="AS50" t="n">
-        <v>245</v>
+        <v>27</v>
       </c>
       <c r="AT50" t="n">
-        <v>245</v>
+        <v>27</v>
       </c>
       <c r="AU50" t="n">
-        <v>245</v>
+        <v>27</v>
       </c>
       <c r="AV50" t="n">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="AW50" t="n">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="AX50" t="n">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="AY50" t="n">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="AZ50" t="n">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="BA50" t="n">
-        <v>248</v>
+        <v>27</v>
       </c>
       <c r="BB50" t="n">
-        <v>248</v>
+        <v>28</v>
       </c>
       <c r="BC50" t="n">
-        <v>248</v>
+        <v>29</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>29</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BG50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BH50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BI50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BJ50" t="n">
+        <v>30</v>
+      </c>
+      <c r="BK50" t="n">
+        <v>38</v>
+      </c>
+      <c r="BL50" t="n">
+        <v>39</v>
+      </c>
+      <c r="BM50" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN50" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO50" t="n">
+        <v>42</v>
+      </c>
+      <c r="BP50" t="n">
+        <v>42</v>
+      </c>
+      <c r="BQ50" t="n">
+        <v>42</v>
+      </c>
+      <c r="BR50" t="n">
+        <v>42</v>
+      </c>
+      <c r="BS50" t="n">
+        <v>42</v>
+      </c>
+      <c r="BT50" t="n">
+        <v>42</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>1285</v>
+        <v>1702</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>zwiebelbrotlive</t>
+          <t>zxkre</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>0</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="I51" t="n">
-        <v>1</v>
+        <v>33</v>
       </c>
       <c r="J51" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="K51" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="L51" t="n">
-        <v>3</v>
+        <v>34</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="P51" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="Q51" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="R51" t="n">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="S51" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="T51" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="U51" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="V51" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="W51" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="X51" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="Y51" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="Z51" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="AA51" t="n">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="AB51" t="n">
-        <v>13</v>
+        <v>53</v>
       </c>
       <c r="AC51" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="AD51" t="n">
-        <v>13</v>
+        <v>54</v>
       </c>
       <c r="AE51" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AF51" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AG51" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AH51" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AI51" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AJ51" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AK51" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AL51" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AM51" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AN51" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="AO51" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="AP51" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AQ51" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AR51" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AS51" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="AT51" t="n">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="AU51" t="n">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="AV51" t="n">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="AW51" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="AX51" t="n">
-        <v>27</v>
+        <v>73</v>
       </c>
       <c r="AY51" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="AZ51" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="BA51" t="n">
-        <v>27</v>
+        <v>78</v>
       </c>
       <c r="BB51" t="n">
-        <v>28</v>
+        <v>79</v>
       </c>
       <c r="BC51" t="n">
-        <v>29</v>
+        <v>79</v>
+      </c>
+      <c r="BD51" t="n">
+        <v>79</v>
+      </c>
+      <c r="BE51" t="n">
+        <v>79</v>
+      </c>
+      <c r="BF51" t="n">
+        <v>80</v>
+      </c>
+      <c r="BG51" t="n">
+        <v>80</v>
+      </c>
+      <c r="BH51" t="n">
+        <v>80</v>
+      </c>
+      <c r="BI51" t="n">
+        <v>80</v>
+      </c>
+      <c r="BJ51" t="n">
+        <v>80</v>
+      </c>
+      <c r="BK51" t="n">
+        <v>82</v>
+      </c>
+      <c r="BL51" t="n">
+        <v>84</v>
+      </c>
+      <c r="BM51" t="n">
+        <v>85</v>
+      </c>
+      <c r="BN51" t="n">
+        <v>85</v>
+      </c>
+      <c r="BO51" t="n">
+        <v>87</v>
+      </c>
+      <c r="BP51" t="n">
+        <v>88</v>
+      </c>
+      <c r="BQ51" t="n">
+        <v>88</v>
+      </c>
+      <c r="BR51" t="n">
+        <v>88</v>
+      </c>
+      <c r="BS51" t="n">
+        <v>91</v>
+      </c>
+      <c r="BT51" t="n">
+        <v>94</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>1286</v>
+        <v>1703</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>zxkre</t>
+          <t>zylandpepstein</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L52" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="n">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="AE52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AF52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AL52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AO52" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="AP52" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AQ52" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AR52" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AS52" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AT52" t="n">
-        <v>71</v>
+        <v>143</v>
       </c>
       <c r="AU52" t="n">
-        <v>71</v>
+        <v>154</v>
       </c>
       <c r="AV52" t="n">
-        <v>72</v>
+        <v>154</v>
       </c>
       <c r="AW52" t="n">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="AX52" t="n">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="AY52" t="n">
-        <v>74</v>
+        <v>154</v>
       </c>
       <c r="AZ52" t="n">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="BA52" t="n">
-        <v>78</v>
+        <v>154</v>
       </c>
       <c r="BB52" t="n">
-        <v>79</v>
+        <v>154</v>
       </c>
       <c r="BC52" t="n">
-        <v>79</v>
+        <v>154</v>
+      </c>
+      <c r="BD52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BE52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BF52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BG52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BH52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BI52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BJ52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BK52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BL52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BM52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BN52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BO52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BP52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BQ52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BR52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BS52" t="n">
+        <v>154</v>
+      </c>
+      <c r="BT52" t="n">
+        <v>154</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>1287</v>
+        <v>1704</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>zylandpepstein</t>
+          <t>zzemiliexx</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -9253,815 +11905,1290 @@
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AO53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AT53" t="n">
-        <v>143</v>
+        <v>24</v>
       </c>
       <c r="AU53" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="AV53" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="AW53" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="AX53" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="AY53" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="AZ53" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="BA53" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="BB53" t="n">
-        <v>154</v>
+        <v>24</v>
       </c>
       <c r="BC53" t="n">
-        <v>154</v>
+        <v>24</v>
+      </c>
+      <c r="BD53" t="n">
+        <v>24</v>
+      </c>
+      <c r="BE53" t="n">
+        <v>24</v>
+      </c>
+      <c r="BF53" t="n">
+        <v>24</v>
+      </c>
+      <c r="BG53" t="n">
+        <v>24</v>
+      </c>
+      <c r="BH53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BI53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BJ53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BK53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BL53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BM53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BN53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BO53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BP53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BQ53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BR53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BS53" t="n">
+        <v>25</v>
+      </c>
+      <c r="BT53" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>1288</v>
+        <v>1705</v>
       </c>
       <c r="B54" t="inlineStr">
+        <is>
+          <t>zzerp</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>16</v>
+      </c>
+      <c r="J54" t="n">
+        <v>16</v>
+      </c>
+      <c r="K54" t="n">
+        <v>16</v>
+      </c>
+      <c r="L54" t="n">
+        <v>16</v>
+      </c>
+      <c r="M54" t="n">
+        <v>17</v>
+      </c>
+      <c r="N54" t="n">
+        <v>17</v>
+      </c>
+      <c r="O54" t="n">
+        <v>17</v>
+      </c>
+      <c r="P54" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>17</v>
+      </c>
+      <c r="R54" t="n">
+        <v>17</v>
+      </c>
+      <c r="S54" t="n">
+        <v>17</v>
+      </c>
+      <c r="T54" t="n">
+        <v>17</v>
+      </c>
+      <c r="U54" t="n">
+        <v>17</v>
+      </c>
+      <c r="V54" t="n">
+        <v>23</v>
+      </c>
+      <c r="W54" t="n">
+        <v>23</v>
+      </c>
+      <c r="X54" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AD54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AE54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AP54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AU54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AV54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AW54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AY54" t="n">
+        <v>23</v>
+      </c>
+      <c r="AZ54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BA54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BB54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BC54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BD54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BF54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BG54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BH54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BI54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BJ54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BK54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BL54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BM54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BN54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BO54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BP54" t="n">
+        <v>23</v>
+      </c>
+      <c r="BQ54" t="n">
+        <v>36</v>
+      </c>
+      <c r="BR54" t="n">
+        <v>36</v>
+      </c>
+      <c r="BS54" t="n">
+        <v>36</v>
+      </c>
+      <c r="BT54" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>1706</v>
+      </c>
+      <c r="B55" t="inlineStr">
         <is>
           <t>محمدحسين</t>
         </is>
       </c>
-      <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="n">
+      <c r="C55" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" t="n">
         <v>39</v>
       </c>
-      <c r="E54" t="n">
+      <c r="E55" t="n">
         <v>39</v>
       </c>
-      <c r="F54" t="n">
+      <c r="F55" t="n">
         <v>39</v>
       </c>
-      <c r="G54" t="n">
+      <c r="G55" t="n">
         <v>39</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H55" t="n">
         <v>39</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>39</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>39</v>
       </c>
-      <c r="K54" t="n">
+      <c r="K55" t="n">
         <v>39</v>
       </c>
-      <c r="L54" t="n">
+      <c r="L55" t="n">
         <v>39</v>
       </c>
-      <c r="M54" t="n">
+      <c r="M55" t="n">
         <v>39</v>
       </c>
-      <c r="N54" t="n">
+      <c r="N55" t="n">
         <v>39</v>
       </c>
-      <c r="O54" t="n">
+      <c r="O55" t="n">
         <v>39</v>
       </c>
-      <c r="P54" t="n">
+      <c r="P55" t="n">
         <v>39</v>
       </c>
-      <c r="Q54" t="n">
+      <c r="Q55" t="n">
         <v>39</v>
       </c>
-      <c r="R54" t="n">
+      <c r="R55" t="n">
         <v>39</v>
       </c>
-      <c r="S54" t="n">
+      <c r="S55" t="n">
         <v>39</v>
       </c>
-      <c r="T54" t="n">
+      <c r="T55" t="n">
         <v>39</v>
       </c>
-      <c r="U54" t="n">
+      <c r="U55" t="n">
         <v>39</v>
       </c>
-      <c r="V54" t="n">
+      <c r="V55" t="n">
         <v>39</v>
       </c>
-      <c r="W54" t="n">
+      <c r="W55" t="n">
         <v>39</v>
       </c>
-      <c r="X54" t="n">
+      <c r="X55" t="n">
         <v>39</v>
       </c>
-      <c r="Y54" t="n">
+      <c r="Y55" t="n">
         <v>39</v>
       </c>
-      <c r="Z54" t="n">
+      <c r="Z55" t="n">
         <v>39</v>
       </c>
-      <c r="AA54" t="n">
+      <c r="AA55" t="n">
         <v>39</v>
       </c>
-      <c r="AB54" t="n">
+      <c r="AB55" t="n">
         <v>39</v>
       </c>
-      <c r="AC54" t="n">
+      <c r="AC55" t="n">
         <v>40</v>
       </c>
-      <c r="AD54" t="n">
+      <c r="AD55" t="n">
         <v>40</v>
       </c>
-      <c r="AE54" t="n">
+      <c r="AE55" t="n">
         <v>40</v>
       </c>
-      <c r="AF54" t="n">
+      <c r="AF55" t="n">
         <v>40</v>
       </c>
-      <c r="AG54" t="n">
+      <c r="AG55" t="n">
         <v>40</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH55" t="n">
         <v>40</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AI55" t="n">
         <v>40</v>
       </c>
-      <c r="AJ54" t="n">
+      <c r="AJ55" t="n">
         <v>40</v>
       </c>
-      <c r="AK54" t="n">
+      <c r="AK55" t="n">
         <v>40</v>
       </c>
-      <c r="AL54" t="n">
+      <c r="AL55" t="n">
         <v>40</v>
       </c>
-      <c r="AM54" t="n">
+      <c r="AM55" t="n">
         <v>40</v>
       </c>
-      <c r="AN54" t="n">
+      <c r="AN55" t="n">
         <v>40</v>
       </c>
-      <c r="AO54" t="n">
+      <c r="AO55" t="n">
         <v>40</v>
       </c>
-      <c r="AP54" t="n">
+      <c r="AP55" t="n">
         <v>40</v>
       </c>
-      <c r="AQ54" t="n">
+      <c r="AQ55" t="n">
         <v>40</v>
       </c>
-      <c r="AR54" t="n">
+      <c r="AR55" t="n">
         <v>40</v>
       </c>
-      <c r="AS54" t="n">
+      <c r="AS55" t="n">
         <v>40</v>
       </c>
-      <c r="AT54" t="n">
+      <c r="AT55" t="n">
         <v>40</v>
       </c>
-      <c r="AU54" t="n">
+      <c r="AU55" t="n">
         <v>40</v>
       </c>
-      <c r="AV54" t="n">
+      <c r="AV55" t="n">
         <v>40</v>
       </c>
-      <c r="AW54" t="n">
+      <c r="AW55" t="n">
         <v>40</v>
       </c>
-      <c r="AX54" t="n">
+      <c r="AX55" t="n">
         <v>40</v>
       </c>
-      <c r="AY54" t="n">
+      <c r="AY55" t="n">
         <v>40</v>
       </c>
-      <c r="AZ54" t="n">
+      <c r="AZ55" t="n">
         <v>40</v>
       </c>
-      <c r="BA54" t="n">
+      <c r="BA55" t="n">
         <v>40</v>
       </c>
-      <c r="BB54" t="n">
+      <c r="BB55" t="n">
         <v>40</v>
       </c>
-      <c r="BC54" t="n">
+      <c r="BC55" t="n">
         <v>40</v>
       </c>
+      <c r="BD55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BE55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BF55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BG55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BH55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BI55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BJ55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BK55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BL55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BM55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BN55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BO55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BP55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BQ55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BR55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BS55" t="n">
+        <v>40</v>
+      </c>
+      <c r="BT55" t="n">
+        <v>40</v>
+      </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="n">
-        <v>1289</v>
-      </c>
-      <c r="B55" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>1707</v>
+      </c>
+      <c r="B56" t="inlineStr">
         <is>
           <t>金龙</t>
         </is>
       </c>
-      <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="n">
-        <v>0</v>
-      </c>
-      <c r="F55" t="n">
+      <c r="C56" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
         <v>1</v>
       </c>
-      <c r="G55" t="n">
+      <c r="G56" t="n">
         <v>1</v>
       </c>
-      <c r="H55" t="n">
+      <c r="H56" t="n">
         <v>11</v>
       </c>
-      <c r="I55" t="n">
+      <c r="I56" t="n">
         <v>20</v>
       </c>
-      <c r="J55" t="n">
+      <c r="J56" t="n">
         <v>20</v>
       </c>
-      <c r="K55" t="n">
+      <c r="K56" t="n">
         <v>21</v>
       </c>
-      <c r="L55" t="n">
+      <c r="L56" t="n">
         <v>21</v>
       </c>
-      <c r="M55" t="n">
+      <c r="M56" t="n">
         <v>21</v>
       </c>
-      <c r="N55" t="n">
+      <c r="N56" t="n">
         <v>21</v>
       </c>
-      <c r="O55" t="n">
+      <c r="O56" t="n">
         <v>21</v>
       </c>
-      <c r="P55" t="n">
+      <c r="P56" t="n">
         <v>21</v>
       </c>
-      <c r="Q55" t="n">
+      <c r="Q56" t="n">
         <v>21</v>
       </c>
-      <c r="R55" t="n">
+      <c r="R56" t="n">
         <v>21</v>
       </c>
-      <c r="S55" t="n">
+      <c r="S56" t="n">
         <v>21</v>
       </c>
-      <c r="T55" t="n">
+      <c r="T56" t="n">
         <v>21</v>
       </c>
-      <c r="U55" t="n">
+      <c r="U56" t="n">
         <v>21</v>
       </c>
-      <c r="V55" t="n">
+      <c r="V56" t="n">
         <v>21</v>
       </c>
-      <c r="W55" t="n">
+      <c r="W56" t="n">
         <v>21</v>
       </c>
-      <c r="X55" t="n">
+      <c r="X56" t="n">
         <v>22</v>
       </c>
-      <c r="Y55" t="n">
+      <c r="Y56" t="n">
         <v>23</v>
       </c>
-      <c r="Z55" t="n">
+      <c r="Z56" t="n">
         <v>24</v>
       </c>
-      <c r="AA55" t="n">
+      <c r="AA56" t="n">
         <v>25</v>
       </c>
-      <c r="AB55" t="n">
+      <c r="AB56" t="n">
         <v>26</v>
       </c>
-      <c r="AC55" t="n">
+      <c r="AC56" t="n">
         <v>27</v>
       </c>
-      <c r="AD55" t="n">
+      <c r="AD56" t="n">
         <v>27</v>
       </c>
-      <c r="AE55" t="n">
+      <c r="AE56" t="n">
         <v>27</v>
       </c>
-      <c r="AF55" t="n">
+      <c r="AF56" t="n">
         <v>27</v>
       </c>
-      <c r="AG55" t="n">
+      <c r="AG56" t="n">
         <v>28</v>
       </c>
-      <c r="AH55" t="n">
+      <c r="AH56" t="n">
         <v>28</v>
       </c>
-      <c r="AI55" t="n">
+      <c r="AI56" t="n">
         <v>28</v>
       </c>
-      <c r="AJ55" t="n">
+      <c r="AJ56" t="n">
         <v>31</v>
       </c>
-      <c r="AK55" t="n">
+      <c r="AK56" t="n">
         <v>31</v>
       </c>
-      <c r="AL55" t="n">
+      <c r="AL56" t="n">
         <v>31</v>
       </c>
-      <c r="AM55" t="n">
+      <c r="AM56" t="n">
         <v>31</v>
       </c>
-      <c r="AN55" t="n">
+      <c r="AN56" t="n">
         <v>31</v>
       </c>
-      <c r="AO55" t="n">
+      <c r="AO56" t="n">
         <v>31</v>
       </c>
-      <c r="AP55" t="n">
+      <c r="AP56" t="n">
         <v>31</v>
       </c>
-      <c r="AQ55" t="n">
+      <c r="AQ56" t="n">
         <v>38</v>
       </c>
-      <c r="AR55" t="n">
+      <c r="AR56" t="n">
         <v>38</v>
       </c>
-      <c r="AS55" t="n">
+      <c r="AS56" t="n">
         <v>39</v>
       </c>
-      <c r="AT55" t="n">
+      <c r="AT56" t="n">
         <v>40</v>
       </c>
-      <c r="AU55" t="n">
+      <c r="AU56" t="n">
         <v>40</v>
       </c>
-      <c r="AV55" t="n">
+      <c r="AV56" t="n">
         <v>40</v>
       </c>
-      <c r="AW55" t="n">
+      <c r="AW56" t="n">
         <v>40</v>
       </c>
-      <c r="AX55" t="n">
+      <c r="AX56" t="n">
         <v>40</v>
       </c>
-      <c r="AY55" t="n">
+      <c r="AY56" t="n">
         <v>56</v>
       </c>
-      <c r="AZ55" t="n">
+      <c r="AZ56" t="n">
         <v>60</v>
       </c>
-      <c r="BA55" t="n">
+      <c r="BA56" t="n">
         <v>60</v>
       </c>
-      <c r="BB55" t="n">
+      <c r="BB56" t="n">
         <v>61</v>
       </c>
-      <c r="BC55" t="n">
+      <c r="BC56" t="n">
         <v>62</v>
       </c>
+      <c r="BD56" t="n">
+        <v>80</v>
+      </c>
+      <c r="BE56" t="n">
+        <v>88</v>
+      </c>
+      <c r="BF56" t="n">
+        <v>88</v>
+      </c>
+      <c r="BG56" t="n">
+        <v>88</v>
+      </c>
+      <c r="BH56" t="n">
+        <v>88</v>
+      </c>
+      <c r="BI56" t="n">
+        <v>88</v>
+      </c>
+      <c r="BJ56" t="n">
+        <v>89</v>
+      </c>
+      <c r="BK56" t="n">
+        <v>91</v>
+      </c>
+      <c r="BL56" t="n">
+        <v>91</v>
+      </c>
+      <c r="BM56" t="n">
+        <v>91</v>
+      </c>
+      <c r="BN56" t="n">
+        <v>91</v>
+      </c>
+      <c r="BO56" t="n">
+        <v>92</v>
+      </c>
+      <c r="BP56" t="n">
+        <v>92</v>
+      </c>
+      <c r="BQ56" t="n">
+        <v>97</v>
+      </c>
+      <c r="BR56" t="n">
+        <v>97</v>
+      </c>
+      <c r="BS56" t="n">
+        <v>97</v>
+      </c>
+      <c r="BT56" t="n">
+        <v>98</v>
+      </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="n">
-        <v>1290</v>
-      </c>
-      <c r="B56" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>1708</v>
+      </c>
+      <c r="B57" t="inlineStr">
         <is>
           <t>빵댕이ㅋ</t>
         </is>
       </c>
-      <c r="C56" t="n">
+      <c r="C57" t="n">
         <v>2</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D57" t="n">
         <v>7</v>
       </c>
-      <c r="E56" t="n">
+      <c r="E57" t="n">
         <v>7</v>
       </c>
-      <c r="F56" t="n">
+      <c r="F57" t="n">
         <v>9</v>
       </c>
-      <c r="G56" t="n">
+      <c r="G57" t="n">
         <v>10</v>
       </c>
-      <c r="H56" t="n">
+      <c r="H57" t="n">
         <v>12</v>
       </c>
-      <c r="I56" t="n">
+      <c r="I57" t="n">
         <v>15</v>
       </c>
-      <c r="J56" t="n">
+      <c r="J57" t="n">
         <v>17</v>
       </c>
-      <c r="K56" t="n">
+      <c r="K57" t="n">
         <v>18</v>
       </c>
-      <c r="L56" t="n">
+      <c r="L57" t="n">
         <v>18</v>
       </c>
-      <c r="M56" t="n">
+      <c r="M57" t="n">
         <v>20</v>
       </c>
-      <c r="N56" t="n">
+      <c r="N57" t="n">
         <v>21</v>
       </c>
-      <c r="O56" t="n">
+      <c r="O57" t="n">
         <v>21</v>
       </c>
-      <c r="P56" t="n">
+      <c r="P57" t="n">
         <v>22</v>
       </c>
-      <c r="Q56" t="n">
+      <c r="Q57" t="n">
         <v>22</v>
       </c>
-      <c r="R56" t="n">
+      <c r="R57" t="n">
         <v>24</v>
       </c>
-      <c r="S56" t="n">
+      <c r="S57" t="n">
         <v>28</v>
       </c>
-      <c r="T56" t="n">
+      <c r="T57" t="n">
         <v>29</v>
       </c>
-      <c r="U56" t="n">
+      <c r="U57" t="n">
         <v>30</v>
       </c>
-      <c r="V56" t="n">
+      <c r="V57" t="n">
         <v>31</v>
       </c>
-      <c r="W56" t="n">
+      <c r="W57" t="n">
         <v>31</v>
       </c>
-      <c r="X56" t="n">
+      <c r="X57" t="n">
         <v>32</v>
       </c>
-      <c r="Y56" t="n">
+      <c r="Y57" t="n">
         <v>33</v>
       </c>
-      <c r="Z56" t="n">
+      <c r="Z57" t="n">
         <v>33</v>
       </c>
-      <c r="AA56" t="n">
+      <c r="AA57" t="n">
         <v>33</v>
       </c>
-      <c r="AB56" t="n">
+      <c r="AB57" t="n">
         <v>34</v>
       </c>
-      <c r="AC56" t="n">
+      <c r="AC57" t="n">
         <v>35</v>
       </c>
-      <c r="AD56" t="n">
+      <c r="AD57" t="n">
         <v>37</v>
       </c>
-      <c r="AE56" t="n">
+      <c r="AE57" t="n">
         <v>37</v>
       </c>
-      <c r="AF56" t="n">
+      <c r="AF57" t="n">
         <v>37</v>
       </c>
-      <c r="AG56" t="n">
+      <c r="AG57" t="n">
         <v>37</v>
       </c>
-      <c r="AH56" t="n">
+      <c r="AH57" t="n">
         <v>37</v>
       </c>
-      <c r="AI56" t="n">
+      <c r="AI57" t="n">
         <v>37</v>
       </c>
-      <c r="AJ56" t="n">
+      <c r="AJ57" t="n">
         <v>38</v>
       </c>
-      <c r="AK56" t="n">
+      <c r="AK57" t="n">
         <v>38</v>
       </c>
-      <c r="AL56" t="n">
+      <c r="AL57" t="n">
         <v>38</v>
       </c>
-      <c r="AM56" t="n">
+      <c r="AM57" t="n">
         <v>38</v>
       </c>
-      <c r="AN56" t="n">
+      <c r="AN57" t="n">
         <v>38</v>
       </c>
-      <c r="AO56" t="n">
+      <c r="AO57" t="n">
         <v>38</v>
       </c>
-      <c r="AP56" t="n">
+      <c r="AP57" t="n">
         <v>39</v>
       </c>
-      <c r="AQ56" t="n">
+      <c r="AQ57" t="n">
         <v>39</v>
       </c>
-      <c r="AR56" t="n">
+      <c r="AR57" t="n">
         <v>40</v>
       </c>
-      <c r="AS56" t="n">
+      <c r="AS57" t="n">
         <v>43</v>
       </c>
-      <c r="AT56" t="n">
+      <c r="AT57" t="n">
         <v>44</v>
       </c>
-      <c r="AU56" t="n">
+      <c r="AU57" t="n">
         <v>45</v>
       </c>
-      <c r="AV56" t="n">
+      <c r="AV57" t="n">
         <v>47</v>
       </c>
-      <c r="AW56" t="n">
+      <c r="AW57" t="n">
         <v>47</v>
       </c>
-      <c r="AX56" t="n">
+      <c r="AX57" t="n">
         <v>48</v>
       </c>
-      <c r="AY56" t="n">
+      <c r="AY57" t="n">
         <v>48</v>
       </c>
-      <c r="AZ56" t="n">
+      <c r="AZ57" t="n">
         <v>49</v>
       </c>
-      <c r="BA56" t="n">
+      <c r="BA57" t="n">
         <v>49</v>
       </c>
-      <c r="BB56" t="n">
+      <c r="BB57" t="n">
         <v>49</v>
       </c>
-      <c r="BC56" t="n">
+      <c r="BC57" t="n">
         <v>49</v>
       </c>
+      <c r="BD57" t="n">
+        <v>49</v>
+      </c>
+      <c r="BE57" t="n">
+        <v>49</v>
+      </c>
+      <c r="BF57" t="n">
+        <v>49</v>
+      </c>
+      <c r="BG57" t="n">
+        <v>49</v>
+      </c>
+      <c r="BH57" t="n">
+        <v>50</v>
+      </c>
+      <c r="BI57" t="n">
+        <v>50</v>
+      </c>
+      <c r="BJ57" t="n">
+        <v>51</v>
+      </c>
+      <c r="BK57" t="n">
+        <v>53</v>
+      </c>
+      <c r="BL57" t="n">
+        <v>54</v>
+      </c>
+      <c r="BM57" t="n">
+        <v>54</v>
+      </c>
+      <c r="BN57" t="n">
+        <v>56</v>
+      </c>
+      <c r="BO57" t="n">
+        <v>58</v>
+      </c>
+      <c r="BP57" t="n">
+        <v>59</v>
+      </c>
+      <c r="BQ57" t="n">
+        <v>61</v>
+      </c>
+      <c r="BR57" t="n">
+        <v>67</v>
+      </c>
+      <c r="BS57" t="n">
+        <v>67</v>
+      </c>
+      <c r="BT57" t="n">
+        <v>68</v>
+      </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="n">
-        <v>1291</v>
-      </c>
-      <c r="B57" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>1709</v>
+      </c>
+      <c r="B58" t="inlineStr">
         <is>
           <t>알래스카해달</t>
         </is>
       </c>
-      <c r="C57" t="n">
+      <c r="C58" t="n">
         <v>95</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D58" t="n">
         <v>95</v>
       </c>
-      <c r="E57" t="n">
+      <c r="E58" t="n">
         <v>95</v>
       </c>
-      <c r="F57" t="n">
+      <c r="F58" t="n">
         <v>193</v>
       </c>
-      <c r="G57" t="n">
+      <c r="G58" t="n">
         <v>193</v>
       </c>
-      <c r="H57" t="n">
+      <c r="H58" t="n">
         <v>272</v>
       </c>
-      <c r="I57" t="n">
+      <c r="I58" t="n">
         <v>274</v>
       </c>
-      <c r="J57" t="n">
+      <c r="J58" t="n">
         <v>274</v>
       </c>
-      <c r="K57" t="n">
+      <c r="K58" t="n">
         <v>302</v>
       </c>
-      <c r="L57" t="n">
+      <c r="L58" t="n">
         <v>358</v>
       </c>
-      <c r="M57" t="n">
+      <c r="M58" t="n">
         <v>426</v>
       </c>
-      <c r="N57" t="n">
+      <c r="N58" t="n">
         <v>426</v>
       </c>
-      <c r="O57" t="n">
+      <c r="O58" t="n">
         <v>426</v>
       </c>
-      <c r="P57" t="n">
+      <c r="P58" t="n">
         <v>436</v>
       </c>
-      <c r="Q57" t="n">
+      <c r="Q58" t="n">
         <v>478</v>
       </c>
-      <c r="R57" t="n">
+      <c r="R58" t="n">
         <v>584</v>
       </c>
-      <c r="S57" t="n">
+      <c r="S58" t="n">
         <v>623</v>
       </c>
-      <c r="T57" t="n">
+      <c r="T58" t="n">
         <v>661</v>
       </c>
-      <c r="U57" t="n">
+      <c r="U58" t="n">
         <v>685</v>
       </c>
-      <c r="V57" t="n">
+      <c r="V58" t="n">
         <v>685</v>
       </c>
-      <c r="W57" t="n">
+      <c r="W58" t="n">
         <v>685</v>
       </c>
-      <c r="X57" t="n">
+      <c r="X58" t="n">
         <v>761</v>
       </c>
-      <c r="Y57" t="n">
+      <c r="Y58" t="n">
         <v>857</v>
       </c>
-      <c r="Z57" t="n">
+      <c r="Z58" t="n">
         <v>879</v>
       </c>
-      <c r="AA57" t="n">
+      <c r="AA58" t="n">
         <v>981</v>
       </c>
-      <c r="AB57" t="n">
+      <c r="AB58" t="n">
         <v>981</v>
       </c>
-      <c r="AC57" t="n">
+      <c r="AC58" t="n">
         <v>1041</v>
       </c>
-      <c r="AD57" t="n">
+      <c r="AD58" t="n">
         <v>1041</v>
       </c>
-      <c r="AE57" t="n">
+      <c r="AE58" t="n">
         <v>1151</v>
       </c>
-      <c r="AF57" t="n">
+      <c r="AF58" t="n">
         <v>1164</v>
       </c>
-      <c r="AG57" t="n">
+      <c r="AG58" t="n">
         <v>1191</v>
       </c>
-      <c r="AH57" t="n">
+      <c r="AH58" t="n">
         <v>1202</v>
       </c>
-      <c r="AI57" t="n">
+      <c r="AI58" t="n">
         <v>1202</v>
       </c>
-      <c r="AJ57" t="n">
+      <c r="AJ58" t="n">
         <v>1202</v>
       </c>
-      <c r="AK57" t="n">
+      <c r="AK58" t="n">
         <v>1230</v>
       </c>
-      <c r="AL57" t="n">
+      <c r="AL58" t="n">
         <v>1282</v>
       </c>
-      <c r="AM57" t="n">
+      <c r="AM58" t="n">
         <v>1313</v>
       </c>
-      <c r="AN57" t="n">
+      <c r="AN58" t="n">
         <v>1313</v>
       </c>
-      <c r="AO57" t="n">
+      <c r="AO58" t="n">
         <v>1330</v>
       </c>
-      <c r="AP57" t="n">
+      <c r="AP58" t="n">
         <v>1330</v>
       </c>
-      <c r="AQ57" t="n">
+      <c r="AQ58" t="n">
         <v>1330</v>
       </c>
-      <c r="AR57" t="n">
+      <c r="AR58" t="n">
         <v>1399</v>
       </c>
-      <c r="AS57" t="n">
+      <c r="AS58" t="n">
         <v>1399</v>
       </c>
-      <c r="AT57" t="n">
+      <c r="AT58" t="n">
         <v>1401</v>
       </c>
-      <c r="AU57" t="n">
+      <c r="AU58" t="n">
         <v>1401</v>
       </c>
-      <c r="AV57" t="n">
+      <c r="AV58" t="n">
         <v>1401</v>
       </c>
-      <c r="AW57" t="n">
+      <c r="AW58" t="n">
         <v>1401</v>
       </c>
-      <c r="AX57" t="n">
+      <c r="AX58" t="n">
         <v>1420</v>
       </c>
-      <c r="AY57" t="n">
+      <c r="AY58" t="n">
         <v>1420</v>
       </c>
-      <c r="AZ57" t="n">
+      <c r="AZ58" t="n">
         <v>1422</v>
       </c>
-      <c r="BA57" t="n">
+      <c r="BA58" t="n">
         <v>1454</v>
       </c>
-      <c r="BB57" t="n">
+      <c r="BB58" t="n">
         <v>1482</v>
       </c>
-      <c r="BC57" t="n">
+      <c r="BC58" t="n">
         <v>1482</v>
+      </c>
+      <c r="BD58" t="n">
+        <v>1517</v>
+      </c>
+      <c r="BE58" t="n">
+        <v>1517</v>
+      </c>
+      <c r="BF58" t="n">
+        <v>1533</v>
+      </c>
+      <c r="BG58" t="n">
+        <v>1533</v>
+      </c>
+      <c r="BH58" t="n">
+        <v>1533</v>
+      </c>
+      <c r="BI58" t="n">
+        <v>1533</v>
+      </c>
+      <c r="BJ58" t="n">
+        <v>1534</v>
+      </c>
+      <c r="BK58" t="n">
+        <v>1535</v>
+      </c>
+      <c r="BL58" t="n">
+        <v>1576</v>
+      </c>
+      <c r="BM58" t="n">
+        <v>1588</v>
+      </c>
+      <c r="BN58" t="n">
+        <v>1588</v>
+      </c>
+      <c r="BO58" t="n">
+        <v>1617</v>
+      </c>
+      <c r="BP58" t="n">
+        <v>1636</v>
+      </c>
+      <c r="BQ58" t="n">
+        <v>1711</v>
+      </c>
+      <c r="BR58" t="n">
+        <v>1758</v>
+      </c>
+      <c r="BS58" t="n">
+        <v>1831</v>
+      </c>
+      <c r="BT58" t="n">
+        <v>1902</v>
       </c>
     </row>
   </sheetData>
